--- a/AAII_Financials/Quarterly/FRSH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FRSH_QTR_FIN.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
   <si>
     <t>FRSH</t>
   </si>
@@ -701,376 +701,389 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18" style="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="18.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18" style="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="18.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="18.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18" style="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="18.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="8">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="8">
         <v>46112</v>
       </c>
-      <c r="E7" s="8">
+      <c r="F7" s="8">
         <v>46022</v>
       </c>
-      <c r="F7" s="8">
+      <c r="G7" s="8">
         <v>45930</v>
       </c>
-      <c r="G7" s="8">
+      <c r="H7" s="8">
         <v>45838</v>
       </c>
-      <c r="H7" s="8">
+      <c r="I7" s="8">
         <v>45747</v>
       </c>
-      <c r="I7" s="8">
+      <c r="J7" s="8">
         <v>45657</v>
       </c>
-      <c r="J7" s="8">
+      <c r="K7" s="8">
         <v>45565</v>
       </c>
-      <c r="K7" s="8">
+      <c r="L7" s="8">
         <v>45473</v>
       </c>
-      <c r="L7" s="8">
+      <c r="M7" s="8">
         <v>45382</v>
       </c>
-      <c r="M7" s="8">
+      <c r="N7" s="8">
         <v>45291</v>
       </c>
-      <c r="N7" s="6">
+      <c r="O7" s="6">
         <v>45199</v>
       </c>
-      <c r="O7" s="6">
+      <c r="P7" s="6">
         <v>45107</v>
       </c>
-      <c r="P7" s="6">
+      <c r="Q7" s="6">
         <v>45016</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="R7" s="6">
         <v>44926</v>
       </c>
-      <c r="R7" s="6">
+      <c r="S7" s="6">
         <v>44834</v>
       </c>
-      <c r="S7" s="6">
+      <c r="T7" s="6">
         <v>44742</v>
       </c>
-      <c r="T7" s="6">
+      <c r="U7" s="6">
         <v>44651</v>
       </c>
-      <c r="U7" s="6">
+      <c r="V7" s="6">
         <v>44561</v>
       </c>
-      <c r="V7" s="3">
+      <c r="W7" s="3">
         <v>44469</v>
       </c>
-      <c r="W7" s="3">
+      <c r="X7" s="3">
         <v>44377</v>
       </c>
-      <c r="X7" s="3">
+      <c r="Y7" s="3">
         <v>44286</v>
       </c>
-      <c r="Y7" s="3">
+      <c r="Z7" s="3">
         <v>44196</v>
       </c>
-      <c r="Z7" s="3">
+      <c r="AA7" s="3">
         <v>44104</v>
       </c>
-      <c r="AA7" s="3">
+      <c r="AB7" s="3">
         <v>44012</v>
       </c>
-      <c r="AB7" s="3">
+      <c r="AC7" s="3">
         <v>43921</v>
       </c>
-      <c r="AC7" s="3">
+      <c r="AD7" s="3">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="9">
+        <v>237400</v>
+      </c>
+      <c r="E8" s="9">
         <v>228600</v>
       </c>
-      <c r="E8" s="9">
+      <c r="F8" s="9">
         <v>222700</v>
       </c>
-      <c r="F8" s="9">
+      <c r="G8" s="9">
         <v>215100</v>
       </c>
-      <c r="G8" s="9">
+      <c r="H8" s="9">
         <v>204700</v>
       </c>
-      <c r="H8" s="9">
+      <c r="I8" s="9">
         <v>196300</v>
       </c>
-      <c r="I8" s="9">
+      <c r="J8" s="9">
         <v>194600</v>
       </c>
-      <c r="J8" s="9">
+      <c r="K8" s="9">
         <v>186600</v>
       </c>
-      <c r="K8" s="9">
+      <c r="L8" s="9">
         <v>174100</v>
       </c>
-      <c r="L8" s="9">
+      <c r="M8" s="9">
         <v>165100</v>
       </c>
-      <c r="M8" s="9">
+      <c r="N8" s="9">
         <v>160100</v>
       </c>
-      <c r="N8" s="7">
+      <c r="O8" s="7">
         <v>153600</v>
       </c>
-      <c r="O8" s="7">
+      <c r="P8" s="7">
         <v>145100</v>
       </c>
-      <c r="P8" s="7">
+      <c r="Q8" s="7">
         <v>137700</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="R8" s="7">
         <v>133200</v>
       </c>
-      <c r="R8" s="7">
+      <c r="S8" s="7">
         <v>128800</v>
       </c>
-      <c r="S8" s="7">
+      <c r="T8" s="7">
         <v>121400</v>
       </c>
-      <c r="T8" s="7">
+      <c r="U8" s="7">
         <v>114600</v>
       </c>
-      <c r="U8" s="7">
+      <c r="V8" s="7">
         <v>105500</v>
       </c>
-      <c r="V8" s="4">
+      <c r="W8" s="4">
         <v>96600</v>
       </c>
-      <c r="W8" s="4">
+      <c r="X8" s="4">
         <v>88300</v>
       </c>
-      <c r="X8" s="4">
+      <c r="Y8" s="4">
         <v>80600</v>
       </c>
-      <c r="Y8" s="4">
+      <c r="Z8" s="4">
         <v>73000</v>
       </c>
-      <c r="Z8" s="4">
+      <c r="AA8" s="4">
         <v>66200</v>
       </c>
-      <c r="AA8" s="4">
+      <c r="AB8" s="4">
         <v>56500</v>
       </c>
-      <c r="AB8" s="4">
+      <c r="AC8" s="4">
         <v>54000</v>
       </c>
-      <c r="AC8" s="4">
+      <c r="AD8" s="4">
         <v>50700</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="9">
+        <v>36100</v>
+      </c>
+      <c r="E9" s="9">
         <v>34700</v>
       </c>
-      <c r="E9" s="9">
+      <c r="F9" s="9">
         <v>32200</v>
       </c>
-      <c r="F9" s="9">
+      <c r="G9" s="9">
         <v>33000</v>
       </c>
-      <c r="G9" s="9">
+      <c r="H9" s="9">
         <v>31100</v>
       </c>
-      <c r="H9" s="9">
+      <c r="I9" s="9">
         <v>29900</v>
       </c>
-      <c r="I9" s="9">
+      <c r="J9" s="9">
         <v>29500</v>
       </c>
-      <c r="J9" s="9">
+      <c r="K9" s="9">
         <v>29800</v>
       </c>
-      <c r="K9" s="9">
+      <c r="L9" s="9">
         <v>28200</v>
       </c>
-      <c r="L9" s="9">
+      <c r="M9" s="9">
         <v>25900</v>
       </c>
-      <c r="M9" s="9">
+      <c r="N9" s="9">
         <v>27000</v>
       </c>
-      <c r="N9" s="7">
+      <c r="O9" s="7">
         <v>26300</v>
       </c>
-      <c r="O9" s="7">
+      <c r="P9" s="7">
         <v>24900</v>
-      </c>
-      <c r="P9" s="7">
-        <v>25200</v>
       </c>
       <c r="Q9" s="7">
         <v>25200</v>
       </c>
       <c r="R9" s="7">
+        <v>25200</v>
+      </c>
+      <c r="S9" s="7">
         <v>24200</v>
       </c>
-      <c r="S9" s="7">
+      <c r="T9" s="7">
         <v>24000</v>
       </c>
-      <c r="T9" s="7">
+      <c r="U9" s="7">
         <v>22400</v>
       </c>
-      <c r="U9" s="7">
+      <c r="V9" s="7">
         <v>20400</v>
       </c>
-      <c r="V9" s="4">
+      <c r="W9" s="4">
         <v>22200</v>
       </c>
-      <c r="W9" s="4">
+      <c r="X9" s="4">
         <v>18700</v>
       </c>
-      <c r="X9" s="4">
+      <c r="Y9" s="4">
         <v>16700</v>
       </c>
-      <c r="Y9" s="4">
+      <c r="Z9" s="4">
         <v>15500</v>
       </c>
-      <c r="Z9" s="4">
+      <c r="AA9" s="4">
         <v>13200</v>
       </c>
-      <c r="AA9" s="4">
+      <c r="AB9" s="4">
         <v>11700</v>
       </c>
-      <c r="AB9" s="4">
+      <c r="AC9" s="4">
         <v>12100</v>
       </c>
-      <c r="AC9" s="4">
+      <c r="AD9" s="4">
         <v>10500</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="9">
+        <v>201300</v>
+      </c>
+      <c r="E10" s="9">
         <v>193900</v>
       </c>
-      <c r="E10" s="9">
+      <c r="F10" s="9">
         <v>190600</v>
       </c>
-      <c r="F10" s="9">
+      <c r="G10" s="9">
         <v>182200</v>
       </c>
-      <c r="G10" s="9">
+      <c r="H10" s="9">
         <v>173500</v>
       </c>
-      <c r="H10" s="9">
+      <c r="I10" s="9">
         <v>166400</v>
       </c>
-      <c r="I10" s="9">
+      <c r="J10" s="9">
         <v>165100</v>
       </c>
-      <c r="J10" s="9">
+      <c r="K10" s="9">
         <v>156800</v>
       </c>
-      <c r="K10" s="9">
+      <c r="L10" s="9">
         <v>146000</v>
       </c>
-      <c r="L10" s="9">
+      <c r="M10" s="9">
         <v>139300</v>
       </c>
-      <c r="M10" s="9">
+      <c r="N10" s="9">
         <v>133100</v>
       </c>
-      <c r="N10" s="7">
+      <c r="O10" s="7">
         <v>127300</v>
       </c>
-      <c r="O10" s="7">
+      <c r="P10" s="7">
         <v>120200</v>
       </c>
-      <c r="P10" s="7">
+      <c r="Q10" s="7">
         <v>112500</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="R10" s="7">
         <v>108000</v>
       </c>
-      <c r="R10" s="7">
+      <c r="S10" s="7">
         <v>104600</v>
       </c>
-      <c r="S10" s="7">
+      <c r="T10" s="7">
         <v>97400</v>
       </c>
-      <c r="T10" s="7">
+      <c r="U10" s="7">
         <v>92200</v>
       </c>
-      <c r="U10" s="7">
+      <c r="V10" s="7">
         <v>85100</v>
       </c>
-      <c r="V10" s="4">
+      <c r="W10" s="4">
         <v>74400</v>
       </c>
-      <c r="W10" s="4">
+      <c r="X10" s="4">
         <v>69600</v>
       </c>
-      <c r="X10" s="4">
+      <c r="Y10" s="4">
         <v>63900</v>
       </c>
-      <c r="Y10" s="4">
+      <c r="Z10" s="4">
         <v>57500</v>
       </c>
-      <c r="Z10" s="4">
+      <c r="AA10" s="4">
         <v>53000</v>
       </c>
-      <c r="AA10" s="4">
+      <c r="AB10" s="4">
         <v>44800</v>
       </c>
-      <c r="AB10" s="4">
+      <c r="AC10" s="4">
         <v>41900</v>
       </c>
-      <c r="AC10" s="4">
+      <c r="AD10" s="4">
         <v>40200</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,7 +1097,7 @@
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
-      <c r="N11" s="7"/>
+      <c r="N11" s="9"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
@@ -1092,7 +1105,7 @@
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
-      <c r="V11" s="4"/>
+      <c r="V11" s="7"/>
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
@@ -1100,91 +1113,95 @@
       <c r="AA11" s="4"/>
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD11" s="4"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="9">
+        <v>43800</v>
+      </c>
+      <c r="E12" s="9">
         <v>49300</v>
       </c>
-      <c r="E12" s="9">
+      <c r="F12" s="9">
         <v>41800</v>
       </c>
-      <c r="F12" s="9">
+      <c r="G12" s="9">
         <v>41500</v>
       </c>
-      <c r="G12" s="9">
+      <c r="H12" s="9">
         <v>39900</v>
       </c>
-      <c r="H12" s="9">
+      <c r="I12" s="9">
         <v>40000</v>
       </c>
-      <c r="I12" s="9">
+      <c r="J12" s="9">
         <v>41000</v>
       </c>
-      <c r="J12" s="9">
+      <c r="K12" s="9">
         <v>47900</v>
       </c>
-      <c r="K12" s="9">
+      <c r="L12" s="9">
         <v>41000</v>
       </c>
-      <c r="L12" s="9">
+      <c r="M12" s="9">
         <v>34700</v>
       </c>
-      <c r="M12" s="9">
+      <c r="N12" s="9">
         <v>35800</v>
       </c>
-      <c r="N12" s="7">
+      <c r="O12" s="7">
         <v>34900</v>
       </c>
-      <c r="O12" s="7">
+      <c r="P12" s="7">
         <v>34200</v>
       </c>
-      <c r="P12" s="7">
+      <c r="Q12" s="7">
         <v>32900</v>
       </c>
-      <c r="Q12" s="7">
+      <c r="R12" s="7">
         <v>34700</v>
       </c>
-      <c r="R12" s="7">
+      <c r="S12" s="7">
         <v>35900</v>
       </c>
-      <c r="S12" s="7">
+      <c r="T12" s="7">
         <v>34300</v>
       </c>
-      <c r="T12" s="7">
+      <c r="U12" s="7">
         <v>30700</v>
       </c>
-      <c r="U12" s="7">
+      <c r="V12" s="7">
         <v>29000</v>
       </c>
-      <c r="V12" s="4">
+      <c r="W12" s="4">
         <v>57100</v>
       </c>
-      <c r="W12" s="4">
+      <c r="X12" s="4">
         <v>18900</v>
       </c>
-      <c r="X12" s="4">
+      <c r="Y12" s="4">
         <v>15400</v>
       </c>
-      <c r="Y12" s="4">
+      <c r="Z12" s="4">
         <v>16100</v>
       </c>
-      <c r="Z12" s="4">
+      <c r="AA12" s="4">
         <v>13200</v>
       </c>
-      <c r="AA12" s="4">
+      <c r="AB12" s="4">
         <v>12300</v>
       </c>
-      <c r="AB12" s="4">
+      <c r="AC12" s="4">
         <v>27500</v>
       </c>
-      <c r="AC12" s="4">
+      <c r="AD12" s="4">
         <v>11400</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1218,7 +1235,7 @@
       <c r="M13" s="9">
         <v>0</v>
       </c>
-      <c r="N13" s="7">
+      <c r="N13" s="9">
         <v>0</v>
       </c>
       <c r="O13" s="7">
@@ -1242,7 +1259,7 @@
       <c r="U13" s="7">
         <v>0</v>
       </c>
-      <c r="V13" s="4">
+      <c r="V13" s="7">
         <v>0</v>
       </c>
       <c r="W13" s="4">
@@ -1266,44 +1283,47 @@
       <c r="AC13" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="9">
-        <v>-900</v>
+        <v>7100</v>
       </c>
       <c r="E14" s="9">
+        <v>-800</v>
+      </c>
+      <c r="F14" s="9">
         <v>-1000</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="9">
         <v>-1500</v>
       </c>
-      <c r="I14" s="9">
+      <c r="J14" s="9">
         <v>8700</v>
       </c>
-      <c r="J14" s="9" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="9">
         <v>-4600</v>
       </c>
-      <c r="M14" s="9">
+      <c r="N14" s="9">
         <v>-3500</v>
       </c>
-      <c r="N14" s="7">
-        <v>0</v>
-      </c>
       <c r="O14" s="7">
         <v>0</v>
       </c>
@@ -1325,7 +1345,7 @@
       <c r="U14" s="7">
         <v>0</v>
       </c>
-      <c r="V14" s="4">
+      <c r="V14" s="7">
         <v>0</v>
       </c>
       <c r="W14" s="4">
@@ -1349,43 +1369,46 @@
       <c r="AC14" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="9">
+        <v>5600</v>
+      </c>
+      <c r="E15" s="9">
         <v>5400</v>
-      </c>
-      <c r="E15" s="9">
-        <v>4500</v>
       </c>
       <c r="F15" s="9">
         <v>4500</v>
       </c>
       <c r="G15" s="9">
+        <v>4500</v>
+      </c>
+      <c r="H15" s="9">
         <v>4600</v>
       </c>
-      <c r="H15" s="9">
+      <c r="I15" s="9">
         <v>4700</v>
-      </c>
-      <c r="I15" s="9">
-        <v>4900</v>
       </c>
       <c r="J15" s="9">
         <v>4900</v>
       </c>
       <c r="K15" s="9">
+        <v>4900</v>
+      </c>
+      <c r="L15" s="9">
         <v>2300</v>
-      </c>
-      <c r="L15" s="9">
-        <v>1600</v>
       </c>
       <c r="M15" s="9">
         <v>1600</v>
       </c>
-      <c r="N15" s="7">
-        <v>0</v>
+      <c r="N15" s="9">
+        <v>1600</v>
       </c>
       <c r="O15" s="7">
         <v>0</v>
@@ -1408,7 +1431,7 @@
       <c r="U15" s="7">
         <v>0</v>
       </c>
-      <c r="V15" s="4">
+      <c r="V15" s="7">
         <v>0</v>
       </c>
       <c r="W15" s="4">
@@ -1432,8 +1455,11 @@
       <c r="AC15" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
@@ -1444,7 +1470,7 @@
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
-      <c r="N16" s="7"/>
+      <c r="N16" s="9"/>
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
@@ -1452,7 +1478,7 @@
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
       <c r="U16" s="7"/>
-      <c r="V16" s="4"/>
+      <c r="V16" s="7"/>
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
@@ -1460,71 +1486,72 @@
       <c r="AA16" s="4"/>
       <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD16" s="4"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="9">
-        <v>236700</v>
+        <v>224200</v>
       </c>
       <c r="E17" s="9">
+        <v>236500</v>
+      </c>
+      <c r="F17" s="9">
         <v>183000</v>
       </c>
-      <c r="F17" s="9">
+      <c r="G17" s="9">
         <v>222600</v>
       </c>
-      <c r="G17" s="9">
+      <c r="H17" s="9">
         <v>213300</v>
       </c>
-      <c r="H17" s="9">
+      <c r="I17" s="9">
         <v>206300</v>
       </c>
-      <c r="I17" s="9">
+      <c r="J17" s="9">
         <v>206600</v>
       </c>
-      <c r="J17" s="9">
+      <c r="K17" s="9">
         <v>225400</v>
       </c>
-      <c r="K17" s="9">
+      <c r="L17" s="9">
         <v>217900</v>
       </c>
-      <c r="L17" s="9">
+      <c r="M17" s="9">
         <v>197300</v>
       </c>
-      <c r="M17" s="9">
+      <c r="N17" s="9">
         <v>200200</v>
       </c>
-      <c r="N17" s="7">
+      <c r="O17" s="7">
         <v>192300</v>
       </c>
-      <c r="O17" s="7">
+      <c r="P17" s="7">
         <v>188400</v>
       </c>
-      <c r="P17" s="7">
+      <c r="Q17" s="7">
         <v>185800</v>
       </c>
-      <c r="Q17" s="7">
+      <c r="R17" s="7">
         <v>193800</v>
       </c>
-      <c r="R17" s="7">
+      <c r="S17" s="7">
         <v>187000</v>
       </c>
-      <c r="S17" s="7">
+      <c r="T17" s="7">
         <v>188800</v>
       </c>
-      <c r="T17" s="7">
+      <c r="U17" s="7">
         <v>161800</v>
       </c>
-      <c r="U17" s="7">
+      <c r="V17" s="7">
         <v>161900</v>
       </c>
-      <c r="V17" s="4">
+      <c r="W17" s="4">
         <v>236900</v>
       </c>
-      <c r="W17" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X17" s="4" t="s">
         <v>8</v>
       </c>
@@ -1543,71 +1570,74 @@
       <c r="AC17" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD17" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="9">
-        <v>-8100</v>
+        <v>13100</v>
       </c>
       <c r="E18" s="9">
+        <v>-7900</v>
+      </c>
+      <c r="F18" s="9">
         <v>39700</v>
       </c>
-      <c r="F18" s="9">
+      <c r="G18" s="9">
         <v>-7500</v>
       </c>
-      <c r="G18" s="9">
+      <c r="H18" s="9">
         <v>-8700</v>
       </c>
-      <c r="H18" s="9">
+      <c r="I18" s="9">
         <v>-10000</v>
       </c>
-      <c r="I18" s="9">
+      <c r="J18" s="9">
         <v>-12000</v>
       </c>
-      <c r="J18" s="9">
+      <c r="K18" s="9">
         <v>-38900</v>
       </c>
-      <c r="K18" s="9">
+      <c r="L18" s="9">
         <v>-43800</v>
       </c>
-      <c r="L18" s="9">
+      <c r="M18" s="9">
         <v>-32200</v>
       </c>
-      <c r="M18" s="9">
+      <c r="N18" s="9">
         <v>-40000</v>
       </c>
-      <c r="N18" s="7">
+      <c r="O18" s="7">
         <v>-38700</v>
       </c>
-      <c r="O18" s="7">
+      <c r="P18" s="7">
         <v>-43300</v>
       </c>
-      <c r="P18" s="7">
+      <c r="Q18" s="7">
         <v>-48100</v>
       </c>
-      <c r="Q18" s="7">
+      <c r="R18" s="7">
         <v>-60600</v>
       </c>
-      <c r="R18" s="7">
+      <c r="S18" s="7">
         <v>-58200</v>
       </c>
-      <c r="S18" s="7">
+      <c r="T18" s="7">
         <v>-67400</v>
       </c>
-      <c r="T18" s="7">
+      <c r="U18" s="7">
         <v>-47200</v>
       </c>
-      <c r="U18" s="7">
+      <c r="V18" s="7">
         <v>-56400</v>
       </c>
-      <c r="V18" s="4">
+      <c r="W18" s="4">
         <v>-140300</v>
       </c>
-      <c r="W18" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X18" s="4" t="s">
         <v>8</v>
       </c>
@@ -1626,8 +1656,11 @@
       <c r="AC18" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD18" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1641,7 +1674,7 @@
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
-      <c r="N19" s="7"/>
+      <c r="N19" s="9"/>
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
@@ -1649,7 +1682,7 @@
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
-      <c r="V19" s="4"/>
+      <c r="V19" s="7"/>
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
       <c r="Y19" s="4"/>
@@ -1657,71 +1690,72 @@
       <c r="AA19" s="4"/>
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD19" s="4"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="9">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="9">
         <v>6500</v>
       </c>
-      <c r="E20" s="9">
+      <c r="F20" s="9">
         <v>1800</v>
       </c>
-      <c r="F20" s="9">
+      <c r="G20" s="9">
         <v>1400</v>
       </c>
-      <c r="G20" s="9">
+      <c r="H20" s="9">
         <v>-2400</v>
       </c>
-      <c r="H20" s="9">
+      <c r="I20" s="9">
         <v>200</v>
       </c>
-      <c r="I20" s="9">
+      <c r="J20" s="9">
         <v>6800</v>
       </c>
-      <c r="J20" s="9">
+      <c r="K20" s="9">
         <v>-1500</v>
       </c>
-      <c r="K20" s="9">
+      <c r="L20" s="9">
         <v>500</v>
       </c>
-      <c r="L20" s="9">
+      <c r="M20" s="9">
         <v>5700</v>
       </c>
-      <c r="M20" s="9">
+      <c r="N20" s="9">
         <v>2000</v>
       </c>
-      <c r="N20" s="7">
+      <c r="O20" s="7">
         <v>10900</v>
       </c>
-      <c r="O20" s="7">
+      <c r="P20" s="7">
         <v>11200</v>
       </c>
-      <c r="P20" s="7">
+      <c r="Q20" s="7">
         <v>9500</v>
       </c>
-      <c r="Q20" s="7">
+      <c r="R20" s="7">
         <v>9900</v>
       </c>
-      <c r="R20" s="7">
+      <c r="S20" s="7">
         <v>2200</v>
       </c>
-      <c r="S20" s="7">
+      <c r="T20" s="7">
         <v>-200</v>
       </c>
-      <c r="T20" s="7">
+      <c r="U20" s="7">
         <v>600</v>
       </c>
-      <c r="U20" s="7">
+      <c r="V20" s="7">
         <v>-100</v>
       </c>
-      <c r="V20" s="4">
+      <c r="W20" s="4">
         <v>22900</v>
       </c>
-      <c r="W20" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X20" s="4" t="s">
         <v>8</v>
       </c>
@@ -1740,71 +1774,74 @@
       <c r="AC20" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD20" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="9">
-        <v>-9200</v>
+        <v>16700</v>
       </c>
       <c r="E21" s="9">
+        <v>-9100</v>
+      </c>
+      <c r="F21" s="9">
         <v>42400</v>
       </c>
-      <c r="F21" s="9">
+      <c r="G21" s="9">
         <v>-4300</v>
       </c>
-      <c r="G21" s="9">
+      <c r="H21" s="9">
         <v>-1600</v>
       </c>
-      <c r="H21" s="9">
+      <c r="I21" s="9">
         <v>-5500</v>
       </c>
-      <c r="I21" s="9">
+      <c r="J21" s="9">
         <v>-13900</v>
       </c>
-      <c r="J21" s="9">
+      <c r="K21" s="9">
         <v>-32400</v>
       </c>
-      <c r="K21" s="9">
+      <c r="L21" s="9">
         <v>-42000</v>
       </c>
-      <c r="L21" s="9">
+      <c r="M21" s="9">
         <v>-36300</v>
       </c>
-      <c r="M21" s="9">
+      <c r="N21" s="9">
         <v>-40400</v>
       </c>
-      <c r="N21" s="7">
+      <c r="O21" s="7">
         <v>-24800</v>
       </c>
-      <c r="O21" s="7">
+      <c r="P21" s="7">
         <v>-29100</v>
       </c>
-      <c r="P21" s="7">
+      <c r="Q21" s="7">
         <v>-35500</v>
       </c>
-      <c r="Q21" s="7">
+      <c r="R21" s="7">
         <v>-47700</v>
       </c>
-      <c r="R21" s="7">
+      <c r="S21" s="7">
         <v>-53200</v>
       </c>
-      <c r="S21" s="7">
+      <c r="T21" s="7">
         <v>-64800</v>
       </c>
-      <c r="T21" s="7">
+      <c r="U21" s="7">
         <v>-43500</v>
       </c>
-      <c r="U21" s="7">
+      <c r="V21" s="7">
         <v>-53000</v>
       </c>
-      <c r="V21" s="4">
+      <c r="W21" s="4">
         <v>-114000</v>
       </c>
-      <c r="W21" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X21" s="4" t="s">
         <v>8</v>
       </c>
@@ -1823,8 +1860,11 @@
       <c r="AC21" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD21" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1858,8 +1898,8 @@
       <c r="M22" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="7">
-        <v>0</v>
+      <c r="N22" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="O22" s="7">
         <v>0</v>
@@ -1882,7 +1922,7 @@
       <c r="U22" s="7">
         <v>0</v>
       </c>
-      <c r="V22" s="4">
+      <c r="V22" s="7">
         <v>0</v>
       </c>
       <c r="W22" s="4">
@@ -1906,174 +1946,183 @@
       <c r="AC22" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="9">
+        <v>10300</v>
+      </c>
+      <c r="E23" s="9">
         <v>-6600</v>
       </c>
-      <c r="E23" s="9">
+      <c r="F23" s="9">
         <v>46900</v>
       </c>
-      <c r="F23" s="9">
+      <c r="G23" s="9">
         <v>-100</v>
       </c>
-      <c r="G23" s="9">
+      <c r="H23" s="9">
         <v>3900</v>
       </c>
-      <c r="H23" s="9">
+      <c r="I23" s="9">
         <v>2600</v>
       </c>
-      <c r="I23" s="9">
+      <c r="J23" s="9">
         <v>-16000</v>
       </c>
-      <c r="J23" s="9">
+      <c r="K23" s="9">
         <v>-24900</v>
       </c>
-      <c r="K23" s="9">
+      <c r="L23" s="9">
         <v>-30500</v>
       </c>
-      <c r="L23" s="9">
+      <c r="M23" s="9">
         <v>-19400</v>
       </c>
-      <c r="M23" s="9">
+      <c r="N23" s="9">
         <v>-25300</v>
       </c>
-      <c r="N23" s="7">
+      <c r="O23" s="7">
         <v>-27700</v>
       </c>
-      <c r="O23" s="7">
+      <c r="P23" s="7">
         <v>-32100</v>
       </c>
-      <c r="P23" s="7">
+      <c r="Q23" s="7">
         <v>-38600</v>
       </c>
-      <c r="Q23" s="7">
+      <c r="R23" s="7">
         <v>-50600</v>
       </c>
-      <c r="R23" s="7">
+      <c r="S23" s="7">
         <v>-56000</v>
       </c>
-      <c r="S23" s="7">
+      <c r="T23" s="7">
         <v>-67600</v>
       </c>
-      <c r="T23" s="7">
+      <c r="U23" s="7">
         <v>-46500</v>
       </c>
-      <c r="U23" s="7">
+      <c r="V23" s="7">
         <v>-56500</v>
       </c>
-      <c r="V23" s="4">
+      <c r="W23" s="4">
         <v>-117300</v>
       </c>
-      <c r="W23" s="4">
+      <c r="X23" s="4">
         <v>-6300</v>
       </c>
-      <c r="X23" s="4">
+      <c r="Y23" s="4">
         <v>-1300</v>
       </c>
-      <c r="Y23" s="4">
+      <c r="Z23" s="4">
         <v>-1400</v>
       </c>
-      <c r="Z23" s="4">
+      <c r="AA23" s="4">
         <v>1300</v>
       </c>
-      <c r="AA23" s="4">
+      <c r="AB23" s="4">
         <v>-3200</v>
       </c>
-      <c r="AB23" s="4">
+      <c r="AC23" s="4">
         <v>-50000</v>
       </c>
-      <c r="AC23" s="4">
+      <c r="AD23" s="4">
         <v>-3600</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="9">
+        <v>7000</v>
+      </c>
+      <c r="E24" s="9">
         <v>-1800</v>
       </c>
-      <c r="E24" s="9">
+      <c r="F24" s="9">
         <v>-144600</v>
       </c>
-      <c r="F24" s="9">
+      <c r="G24" s="9">
         <v>4600</v>
       </c>
-      <c r="G24" s="9">
+      <c r="H24" s="9">
         <v>5600</v>
       </c>
-      <c r="H24" s="9">
+      <c r="I24" s="9">
         <v>3900</v>
       </c>
-      <c r="I24" s="9">
+      <c r="J24" s="9">
         <v>5900</v>
       </c>
-      <c r="J24" s="9">
+      <c r="K24" s="9">
         <v>5000</v>
       </c>
-      <c r="K24" s="9">
+      <c r="L24" s="9">
         <v>-10400</v>
       </c>
-      <c r="L24" s="9">
+      <c r="M24" s="9">
         <v>4000</v>
       </c>
-      <c r="M24" s="9">
+      <c r="N24" s="9">
         <v>2800</v>
       </c>
-      <c r="N24" s="7">
+      <c r="O24" s="7">
         <v>3300</v>
       </c>
-      <c r="O24" s="7">
+      <c r="P24" s="7">
         <v>3600</v>
       </c>
-      <c r="P24" s="7">
+      <c r="Q24" s="7">
         <v>4000</v>
       </c>
-      <c r="Q24" s="7">
+      <c r="R24" s="7">
         <v>4800</v>
       </c>
-      <c r="R24" s="7">
+      <c r="S24" s="7">
         <v>1800</v>
       </c>
-      <c r="S24" s="7">
+      <c r="T24" s="7">
         <v>2200</v>
       </c>
-      <c r="T24" s="7">
+      <c r="U24" s="7">
         <v>2500</v>
       </c>
-      <c r="U24" s="7">
+      <c r="V24" s="7">
         <v>18200</v>
       </c>
-      <c r="V24" s="4">
+      <c r="W24" s="4">
         <v>-9900</v>
-      </c>
-      <c r="W24" s="4">
-        <v>1100</v>
       </c>
       <c r="X24" s="4">
         <v>1100</v>
       </c>
       <c r="Y24" s="4">
+        <v>1100</v>
+      </c>
+      <c r="Z24" s="4">
         <v>100</v>
       </c>
-      <c r="Z24" s="4">
+      <c r="AA24" s="4">
         <v>-100</v>
       </c>
-      <c r="AA24" s="4">
+      <c r="AB24" s="4">
         <v>200</v>
       </c>
-      <c r="AB24" s="4">
+      <c r="AC24" s="4">
         <v>3800</v>
       </c>
-      <c r="AC24" s="4">
+      <c r="AD24" s="4">
         <v>600</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2107,7 +2156,7 @@
       <c r="M25" s="9">
         <v>0</v>
       </c>
-      <c r="N25" s="7">
+      <c r="N25" s="9">
         <v>0</v>
       </c>
       <c r="O25" s="7">
@@ -2131,7 +2180,7 @@
       <c r="U25" s="7">
         <v>0</v>
       </c>
-      <c r="V25" s="4">
+      <c r="V25" s="7">
         <v>0</v>
       </c>
       <c r="W25" s="4">
@@ -2155,71 +2204,74 @@
       <c r="AC25" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="9">
+        <v>3200</v>
+      </c>
+      <c r="E26" s="9">
         <v>-4800</v>
       </c>
-      <c r="E26" s="9">
+      <c r="F26" s="9">
         <v>191400</v>
       </c>
-      <c r="F26" s="9">
+      <c r="G26" s="9">
         <v>-4700</v>
       </c>
-      <c r="G26" s="9">
+      <c r="H26" s="9">
         <v>-1700</v>
       </c>
-      <c r="H26" s="9">
+      <c r="I26" s="9">
         <v>-1300</v>
       </c>
-      <c r="I26" s="9">
+      <c r="J26" s="9">
         <v>-21900</v>
       </c>
-      <c r="J26" s="9">
+      <c r="K26" s="9">
         <v>-30000</v>
       </c>
-      <c r="K26" s="9">
+      <c r="L26" s="9">
         <v>-20200</v>
       </c>
-      <c r="L26" s="9">
+      <c r="M26" s="9">
         <v>-23300</v>
       </c>
-      <c r="M26" s="9">
+      <c r="N26" s="9">
         <v>-28100</v>
       </c>
-      <c r="N26" s="7">
+      <c r="O26" s="7">
         <v>-31000</v>
       </c>
-      <c r="O26" s="7">
+      <c r="P26" s="7">
         <v>-35700</v>
       </c>
-      <c r="P26" s="7">
+      <c r="Q26" s="7">
         <v>-42700</v>
       </c>
-      <c r="Q26" s="7">
+      <c r="R26" s="7">
         <v>-55500</v>
       </c>
-      <c r="R26" s="7">
+      <c r="S26" s="7">
         <v>-57800</v>
       </c>
-      <c r="S26" s="7">
+      <c r="T26" s="7">
         <v>-69800</v>
       </c>
-      <c r="T26" s="7">
+      <c r="U26" s="7">
         <v>-49100</v>
       </c>
-      <c r="U26" s="7">
+      <c r="V26" s="7">
         <v>-74700</v>
       </c>
-      <c r="V26" s="4">
+      <c r="W26" s="4">
         <v>-107400</v>
       </c>
-      <c r="W26" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X26" s="4" t="s">
         <v>8</v>
       </c>
@@ -2238,71 +2290,74 @@
       <c r="AC26" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD26" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="9">
+        <v>3200</v>
+      </c>
+      <c r="E27" s="9">
         <v>-4800</v>
       </c>
-      <c r="E27" s="9">
+      <c r="F27" s="9">
         <v>191400</v>
       </c>
-      <c r="F27" s="9">
+      <c r="G27" s="9">
         <v>-4700</v>
       </c>
-      <c r="G27" s="9">
+      <c r="H27" s="9">
         <v>-1700</v>
       </c>
-      <c r="H27" s="9">
+      <c r="I27" s="9">
         <v>-1300</v>
       </c>
-      <c r="I27" s="9">
+      <c r="J27" s="9">
         <v>-21900</v>
       </c>
-      <c r="J27" s="9">
+      <c r="K27" s="9">
         <v>-30000</v>
       </c>
-      <c r="K27" s="9">
+      <c r="L27" s="9">
         <v>-20200</v>
       </c>
-      <c r="L27" s="9">
+      <c r="M27" s="9">
         <v>-23300</v>
       </c>
-      <c r="M27" s="9">
+      <c r="N27" s="9">
         <v>-28100</v>
       </c>
-      <c r="N27" s="7">
+      <c r="O27" s="7">
         <v>-31000</v>
       </c>
-      <c r="O27" s="7">
+      <c r="P27" s="7">
         <v>-35700</v>
       </c>
-      <c r="P27" s="7">
+      <c r="Q27" s="7">
         <v>-42700</v>
       </c>
-      <c r="Q27" s="7">
+      <c r="R27" s="7">
         <v>-55500</v>
       </c>
-      <c r="R27" s="7">
+      <c r="S27" s="7">
         <v>-57800</v>
       </c>
-      <c r="S27" s="7">
+      <c r="T27" s="7">
         <v>-69800</v>
       </c>
-      <c r="T27" s="7">
+      <c r="U27" s="7">
         <v>-49100</v>
       </c>
-      <c r="U27" s="7">
+      <c r="V27" s="7">
         <v>-74700</v>
       </c>
-      <c r="V27" s="4">
+      <c r="W27" s="4">
         <v>-2372300</v>
       </c>
-      <c r="W27" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X27" s="4" t="s">
         <v>8</v>
       </c>
@@ -2321,8 +2376,11 @@
       <c r="AC27" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD27" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2356,7 +2414,7 @@
       <c r="M28" s="9">
         <v>0</v>
       </c>
-      <c r="N28" s="7">
+      <c r="N28" s="9">
         <v>0</v>
       </c>
       <c r="O28" s="7">
@@ -2380,7 +2438,7 @@
       <c r="U28" s="7">
         <v>0</v>
       </c>
-      <c r="V28" s="4">
+      <c r="V28" s="7">
         <v>0</v>
       </c>
       <c r="W28" s="4">
@@ -2404,8 +2462,11 @@
       <c r="AC28" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD28" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2439,7 +2500,7 @@
       <c r="M29" s="9">
         <v>0</v>
       </c>
-      <c r="N29" s="7">
+      <c r="N29" s="9">
         <v>0</v>
       </c>
       <c r="O29" s="7">
@@ -2463,7 +2524,7 @@
       <c r="U29" s="7">
         <v>0</v>
       </c>
-      <c r="V29" s="4">
+      <c r="V29" s="7">
         <v>0</v>
       </c>
       <c r="W29" s="4">
@@ -2487,8 +2548,11 @@
       <c r="AC29" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2522,7 +2586,7 @@
       <c r="M30" s="9">
         <v>0</v>
       </c>
-      <c r="N30" s="7">
+      <c r="N30" s="9">
         <v>0</v>
       </c>
       <c r="O30" s="7">
@@ -2546,7 +2610,7 @@
       <c r="U30" s="7">
         <v>0</v>
       </c>
-      <c r="V30" s="4">
+      <c r="V30" s="7">
         <v>0</v>
       </c>
       <c r="W30" s="4">
@@ -2570,8 +2634,11 @@
       <c r="AC30" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2605,7 +2672,7 @@
       <c r="M31" s="9">
         <v>0</v>
       </c>
-      <c r="N31" s="7">
+      <c r="N31" s="9">
         <v>0</v>
       </c>
       <c r="O31" s="7">
@@ -2629,7 +2696,7 @@
       <c r="U31" s="7">
         <v>0</v>
       </c>
-      <c r="V31" s="4">
+      <c r="V31" s="7">
         <v>0</v>
       </c>
       <c r="W31" s="4">
@@ -2653,71 +2720,74 @@
       <c r="AC31" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="9">
+        <v>-2000</v>
+      </c>
+      <c r="E32" s="9">
         <v>-6500</v>
       </c>
-      <c r="E32" s="9">
+      <c r="F32" s="9">
         <v>-1800</v>
       </c>
-      <c r="F32" s="9">
+      <c r="G32" s="9">
         <v>-1400</v>
       </c>
-      <c r="G32" s="9">
+      <c r="H32" s="9">
         <v>2400</v>
       </c>
-      <c r="H32" s="9">
+      <c r="I32" s="9">
         <v>-200</v>
       </c>
-      <c r="I32" s="9">
+      <c r="J32" s="9">
         <v>-6800</v>
       </c>
-      <c r="J32" s="9">
+      <c r="K32" s="9">
         <v>1500</v>
       </c>
-      <c r="K32" s="9">
+      <c r="L32" s="9">
         <v>-500</v>
       </c>
-      <c r="L32" s="9">
+      <c r="M32" s="9">
         <v>-5700</v>
       </c>
-      <c r="M32" s="9">
+      <c r="N32" s="9">
         <v>-2000</v>
       </c>
-      <c r="N32" s="7">
+      <c r="O32" s="7">
         <v>-10900</v>
       </c>
-      <c r="O32" s="7">
+      <c r="P32" s="7">
         <v>-11200</v>
       </c>
-      <c r="P32" s="7">
+      <c r="Q32" s="7">
         <v>-9500</v>
       </c>
-      <c r="Q32" s="7">
+      <c r="R32" s="7">
         <v>-9900</v>
       </c>
-      <c r="R32" s="7">
+      <c r="S32" s="7">
         <v>-2200</v>
       </c>
-      <c r="S32" s="7">
+      <c r="T32" s="7">
         <v>200</v>
       </c>
-      <c r="T32" s="7">
+      <c r="U32" s="7">
         <v>-600</v>
       </c>
-      <c r="U32" s="7">
+      <c r="V32" s="7">
         <v>100</v>
       </c>
-      <c r="V32" s="4">
+      <c r="W32" s="4">
         <v>-22900</v>
       </c>
-      <c r="W32" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X32" s="4" t="s">
         <v>8</v>
       </c>
@@ -2736,71 +2806,74 @@
       <c r="AC32" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD32" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="9">
+        <v>3200</v>
+      </c>
+      <c r="E33" s="9">
         <v>-4800</v>
       </c>
-      <c r="E33" s="9">
+      <c r="F33" s="9">
         <v>191400</v>
       </c>
-      <c r="F33" s="9">
+      <c r="G33" s="9">
         <v>-4700</v>
       </c>
-      <c r="G33" s="9">
+      <c r="H33" s="9">
         <v>-1700</v>
       </c>
-      <c r="H33" s="9">
+      <c r="I33" s="9">
         <v>-1300</v>
       </c>
-      <c r="I33" s="9">
+      <c r="J33" s="9">
         <v>-21900</v>
       </c>
-      <c r="J33" s="9">
+      <c r="K33" s="9">
         <v>-30000</v>
       </c>
-      <c r="K33" s="9">
+      <c r="L33" s="9">
         <v>-20200</v>
       </c>
-      <c r="L33" s="9">
+      <c r="M33" s="9">
         <v>-23300</v>
       </c>
-      <c r="M33" s="9">
+      <c r="N33" s="9">
         <v>-28100</v>
       </c>
-      <c r="N33" s="7">
+      <c r="O33" s="7">
         <v>-31000</v>
       </c>
-      <c r="O33" s="7">
+      <c r="P33" s="7">
         <v>-35700</v>
       </c>
-      <c r="P33" s="7">
+      <c r="Q33" s="7">
         <v>-42700</v>
       </c>
-      <c r="Q33" s="7">
+      <c r="R33" s="7">
         <v>-55500</v>
       </c>
-      <c r="R33" s="7">
+      <c r="S33" s="7">
         <v>-57800</v>
       </c>
-      <c r="S33" s="7">
+      <c r="T33" s="7">
         <v>-69800</v>
       </c>
-      <c r="T33" s="7">
+      <c r="U33" s="7">
         <v>-49100</v>
       </c>
-      <c r="U33" s="7">
+      <c r="V33" s="7">
         <v>-74700</v>
       </c>
-      <c r="V33" s="4">
+      <c r="W33" s="4">
         <v>-2372300</v>
       </c>
-      <c r="W33" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X33" s="4" t="s">
         <v>8</v>
       </c>
@@ -2819,8 +2892,11 @@
       <c r="AC33" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD33" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2854,7 +2930,7 @@
       <c r="M34" s="9">
         <v>0</v>
       </c>
-      <c r="N34" s="7">
+      <c r="N34" s="9">
         <v>0</v>
       </c>
       <c r="O34" s="7">
@@ -2878,7 +2954,7 @@
       <c r="U34" s="7">
         <v>0</v>
       </c>
-      <c r="V34" s="4">
+      <c r="V34" s="7">
         <v>0</v>
       </c>
       <c r="W34" s="4">
@@ -2902,71 +2978,74 @@
       <c r="AC34" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD34" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="9">
+        <v>3200</v>
+      </c>
+      <c r="E35" s="9">
         <v>-4800</v>
       </c>
-      <c r="E35" s="9">
+      <c r="F35" s="9">
         <v>191400</v>
       </c>
-      <c r="F35" s="9">
+      <c r="G35" s="9">
         <v>-4700</v>
       </c>
-      <c r="G35" s="9">
+      <c r="H35" s="9">
         <v>-1700</v>
       </c>
-      <c r="H35" s="9">
+      <c r="I35" s="9">
         <v>-1300</v>
       </c>
-      <c r="I35" s="9">
+      <c r="J35" s="9">
         <v>-21900</v>
       </c>
-      <c r="J35" s="9">
+      <c r="K35" s="9">
         <v>-30000</v>
       </c>
-      <c r="K35" s="9">
+      <c r="L35" s="9">
         <v>-20200</v>
       </c>
-      <c r="L35" s="9">
+      <c r="M35" s="9">
         <v>-23300</v>
       </c>
-      <c r="M35" s="9">
+      <c r="N35" s="9">
         <v>-28100</v>
       </c>
-      <c r="N35" s="7">
+      <c r="O35" s="7">
         <v>-31000</v>
       </c>
-      <c r="O35" s="7">
+      <c r="P35" s="7">
         <v>-35700</v>
       </c>
-      <c r="P35" s="7">
+      <c r="Q35" s="7">
         <v>-42700</v>
       </c>
-      <c r="Q35" s="7">
+      <c r="R35" s="7">
         <v>-55500</v>
       </c>
-      <c r="R35" s="7">
+      <c r="S35" s="7">
         <v>-57800</v>
       </c>
-      <c r="S35" s="7">
+      <c r="T35" s="7">
         <v>-69800</v>
       </c>
-      <c r="T35" s="7">
+      <c r="U35" s="7">
         <v>-49100</v>
       </c>
-      <c r="U35" s="7">
+      <c r="V35" s="7">
         <v>-74700</v>
       </c>
-      <c r="V35" s="4">
+      <c r="W35" s="4">
         <v>-2372300</v>
       </c>
-      <c r="W35" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X35" s="4" t="s">
         <v>8</v>
       </c>
@@ -2985,96 +3064,102 @@
       <c r="AC35" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD35" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="8">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="8">
         <v>46112</v>
       </c>
-      <c r="E38" s="8">
+      <c r="F38" s="8">
         <v>46022</v>
       </c>
-      <c r="F38" s="8">
+      <c r="G38" s="8">
         <v>45930</v>
       </c>
-      <c r="G38" s="8">
+      <c r="H38" s="8">
         <v>45838</v>
       </c>
-      <c r="H38" s="8">
+      <c r="I38" s="8">
         <v>45747</v>
       </c>
-      <c r="I38" s="8">
+      <c r="J38" s="8">
         <v>45657</v>
       </c>
-      <c r="J38" s="8">
+      <c r="K38" s="8">
         <v>45565</v>
       </c>
-      <c r="K38" s="8">
+      <c r="L38" s="8">
         <v>45473</v>
       </c>
-      <c r="L38" s="8">
+      <c r="M38" s="8">
         <v>45382</v>
       </c>
-      <c r="M38" s="8">
+      <c r="N38" s="8">
         <v>45291</v>
       </c>
-      <c r="N38" s="6">
+      <c r="O38" s="6">
         <v>45199</v>
       </c>
-      <c r="O38" s="6">
+      <c r="P38" s="6">
         <v>45107</v>
       </c>
-      <c r="P38" s="6">
+      <c r="Q38" s="6">
         <v>45016</v>
       </c>
-      <c r="Q38" s="6">
+      <c r="R38" s="6">
         <v>44926</v>
       </c>
-      <c r="R38" s="6">
+      <c r="S38" s="6">
         <v>44834</v>
       </c>
-      <c r="S38" s="6">
+      <c r="T38" s="6">
         <v>44742</v>
       </c>
-      <c r="T38" s="6">
+      <c r="U38" s="6">
         <v>44651</v>
       </c>
-      <c r="U38" s="6">
+      <c r="V38" s="6">
         <v>44561</v>
       </c>
-      <c r="V38" s="3">
+      <c r="W38" s="3">
         <v>44469</v>
       </c>
-      <c r="W38" s="3">
+      <c r="X38" s="3">
         <v>44377</v>
       </c>
-      <c r="X38" s="3">
+      <c r="Y38" s="3">
         <v>44286</v>
       </c>
-      <c r="Y38" s="3">
+      <c r="Z38" s="3">
         <v>44196</v>
       </c>
-      <c r="Z38" s="3">
+      <c r="AA38" s="3">
         <v>44104</v>
       </c>
-      <c r="AA38" s="3">
+      <c r="AB38" s="3">
         <v>44012</v>
       </c>
-      <c r="AB38" s="3">
+      <c r="AC38" s="3">
         <v>43921</v>
       </c>
-      <c r="AC38" s="3">
+      <c r="AD38" s="3">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3088,7 +3173,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="9"/>
       <c r="M39" s="9"/>
-      <c r="N39" s="7"/>
+      <c r="N39" s="9"/>
       <c r="O39" s="7"/>
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
@@ -3096,7 +3181,7 @@
       <c r="S39" s="7"/>
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
-      <c r="V39" s="4"/>
+      <c r="V39" s="7"/>
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
       <c r="Y39" s="4"/>
@@ -3104,8 +3189,9 @@
       <c r="AA39" s="4"/>
       <c r="AB39" s="4"/>
       <c r="AC39" s="4"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD39" s="4"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3119,7 +3205,7 @@
       <c r="K40" s="9"/>
       <c r="L40" s="9"/>
       <c r="M40" s="9"/>
-      <c r="N40" s="7"/>
+      <c r="N40" s="9"/>
       <c r="O40" s="7"/>
       <c r="P40" s="7"/>
       <c r="Q40" s="7"/>
@@ -3127,7 +3213,7 @@
       <c r="S40" s="7"/>
       <c r="T40" s="7"/>
       <c r="U40" s="7"/>
-      <c r="V40" s="4"/>
+      <c r="V40" s="7"/>
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
       <c r="Y40" s="4"/>
@@ -3135,74 +3221,75 @@
       <c r="AA40" s="4"/>
       <c r="AB40" s="4"/>
       <c r="AC40" s="4"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD40" s="4"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="9">
+        <v>494700</v>
+      </c>
+      <c r="E41" s="9">
         <v>548200</v>
       </c>
-      <c r="E41" s="9">
+      <c r="F41" s="9">
         <v>569800</v>
       </c>
-      <c r="F41" s="9">
+      <c r="G41" s="9">
         <v>420900</v>
       </c>
-      <c r="G41" s="9">
+      <c r="H41" s="9">
         <v>486000</v>
       </c>
-      <c r="H41" s="9">
+      <c r="I41" s="9">
         <v>594200</v>
       </c>
-      <c r="I41" s="9">
+      <c r="J41" s="9">
         <v>620300</v>
       </c>
-      <c r="J41" s="9">
+      <c r="K41" s="9">
         <v>391100</v>
       </c>
-      <c r="K41" s="9">
+      <c r="L41" s="9">
         <v>310300</v>
       </c>
-      <c r="L41" s="9">
+      <c r="M41" s="9">
         <v>468000</v>
       </c>
-      <c r="M41" s="9">
+      <c r="N41" s="9">
         <v>488100</v>
       </c>
-      <c r="N41" s="7">
+      <c r="O41" s="7">
         <v>458200</v>
       </c>
-      <c r="O41" s="7">
+      <c r="P41" s="7">
         <v>356200</v>
       </c>
-      <c r="P41" s="7">
+      <c r="Q41" s="7">
         <v>344500</v>
       </c>
-      <c r="Q41" s="7">
+      <c r="R41" s="7">
         <v>304100</v>
       </c>
-      <c r="R41" s="7">
+      <c r="S41" s="7">
         <v>432300</v>
       </c>
-      <c r="S41" s="7">
+      <c r="T41" s="7">
         <v>590100</v>
       </c>
-      <c r="T41" s="7">
+      <c r="U41" s="7">
         <v>603500</v>
       </c>
-      <c r="U41" s="7">
+      <c r="V41" s="7">
         <v>747900</v>
       </c>
-      <c r="V41" s="4">
+      <c r="W41" s="4">
         <v>1180000</v>
       </c>
-      <c r="W41" s="4">
+      <c r="X41" s="4">
         <v>104800</v>
       </c>
-      <c r="X41" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y41" s="4" t="s">
         <v>8</v>
       </c>
@@ -3218,74 +3305,77 @@
       <c r="AC41" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD41" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="9">
+        <v>169400</v>
+      </c>
+      <c r="E42" s="9">
         <v>231100</v>
       </c>
-      <c r="E42" s="9">
+      <c r="F42" s="9">
         <v>211600</v>
       </c>
-      <c r="F42" s="9">
+      <c r="G42" s="9">
         <v>392300</v>
       </c>
-      <c r="G42" s="9">
+      <c r="H42" s="9">
         <v>440200</v>
       </c>
-      <c r="H42" s="9">
+      <c r="I42" s="9">
         <v>401100</v>
       </c>
-      <c r="I42" s="9">
+      <c r="J42" s="9">
         <v>449800</v>
       </c>
-      <c r="J42" s="9">
+      <c r="K42" s="9">
         <v>663900</v>
       </c>
-      <c r="K42" s="9">
+      <c r="L42" s="9">
         <v>708800</v>
       </c>
-      <c r="L42" s="9">
+      <c r="M42" s="9">
         <v>739300</v>
       </c>
-      <c r="M42" s="9">
+      <c r="N42" s="9">
         <v>699500</v>
       </c>
-      <c r="N42" s="7">
+      <c r="O42" s="7">
         <v>706500</v>
       </c>
-      <c r="O42" s="7">
+      <c r="P42" s="7">
         <v>804600</v>
       </c>
-      <c r="P42" s="7">
+      <c r="Q42" s="7">
         <v>806100</v>
       </c>
-      <c r="Q42" s="7">
+      <c r="R42" s="7">
         <v>843400</v>
       </c>
-      <c r="R42" s="7">
+      <c r="S42" s="7">
         <v>719200</v>
       </c>
-      <c r="S42" s="7">
+      <c r="T42" s="7">
         <v>584000</v>
       </c>
-      <c r="T42" s="7">
+      <c r="U42" s="7">
         <v>594300</v>
       </c>
-      <c r="U42" s="7">
+      <c r="V42" s="7">
         <v>575700</v>
       </c>
-      <c r="V42" s="4">
+      <c r="W42" s="4">
         <v>146600</v>
       </c>
-      <c r="W42" s="4">
+      <c r="X42" s="4">
         <v>135800</v>
       </c>
-      <c r="X42" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y42" s="4" t="s">
         <v>8</v>
       </c>
@@ -3301,74 +3391,77 @@
       <c r="AC42" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD42" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="9">
+        <v>138400</v>
+      </c>
+      <c r="E43" s="9">
         <v>128400</v>
       </c>
-      <c r="E43" s="9">
+      <c r="F43" s="9">
         <v>152300</v>
       </c>
-      <c r="F43" s="9">
+      <c r="G43" s="9">
         <v>122000</v>
       </c>
-      <c r="G43" s="9">
+      <c r="H43" s="9">
         <v>118700</v>
       </c>
-      <c r="H43" s="9">
+      <c r="I43" s="9">
         <v>115500</v>
       </c>
-      <c r="I43" s="9">
+      <c r="J43" s="9">
         <v>126200</v>
       </c>
-      <c r="J43" s="9">
+      <c r="K43" s="9">
         <v>103300</v>
       </c>
-      <c r="K43" s="9">
+      <c r="L43" s="9">
         <v>105200</v>
       </c>
-      <c r="L43" s="9">
+      <c r="M43" s="9">
         <v>88200</v>
       </c>
-      <c r="M43" s="9">
+      <c r="N43" s="9">
         <v>101600</v>
       </c>
-      <c r="N43" s="7">
+      <c r="O43" s="7">
         <v>80300</v>
       </c>
-      <c r="O43" s="7">
+      <c r="P43" s="7">
         <v>73900</v>
       </c>
-      <c r="P43" s="7">
+      <c r="Q43" s="7">
         <v>72800</v>
       </c>
-      <c r="Q43" s="7">
+      <c r="R43" s="7">
         <v>70500</v>
       </c>
-      <c r="R43" s="7">
+      <c r="S43" s="7">
         <v>56800</v>
       </c>
-      <c r="S43" s="7">
+      <c r="T43" s="7">
         <v>55400</v>
       </c>
-      <c r="T43" s="7">
+      <c r="U43" s="7">
         <v>48500</v>
       </c>
-      <c r="U43" s="7">
+      <c r="V43" s="7">
         <v>51800</v>
       </c>
-      <c r="V43" s="4">
+      <c r="W43" s="4">
         <v>44300</v>
       </c>
-      <c r="W43" s="4">
+      <c r="X43" s="4">
         <v>40400</v>
       </c>
-      <c r="X43" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y43" s="4" t="s">
         <v>8</v>
       </c>
@@ -3384,8 +3477,11 @@
       <c r="AC43" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD43" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3419,8 +3515,8 @@
       <c r="M44" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="N44" s="7">
-        <v>0</v>
+      <c r="N44" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="O44" s="7">
         <v>0</v>
@@ -3443,7 +3539,7 @@
       <c r="U44" s="7">
         <v>0</v>
       </c>
-      <c r="V44" s="4">
+      <c r="V44" s="7">
         <v>0</v>
       </c>
       <c r="W44" s="4">
@@ -3467,74 +3563,77 @@
       <c r="AC44" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD44" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="9">
+        <v>32100</v>
+      </c>
+      <c r="E45" s="9">
         <v>30900</v>
       </c>
-      <c r="E45" s="9">
+      <c r="F45" s="9">
         <v>48200</v>
       </c>
-      <c r="F45" s="9">
+      <c r="G45" s="9">
         <v>28500</v>
       </c>
-      <c r="G45" s="9">
+      <c r="H45" s="9">
         <v>27500</v>
       </c>
-      <c r="H45" s="9">
+      <c r="I45" s="9">
         <v>26500</v>
       </c>
-      <c r="I45" s="9">
+      <c r="J45" s="9">
         <v>26100</v>
       </c>
-      <c r="J45" s="9">
+      <c r="K45" s="9">
         <v>25100</v>
       </c>
-      <c r="K45" s="9">
+      <c r="L45" s="9">
         <v>24500</v>
       </c>
-      <c r="L45" s="9">
+      <c r="M45" s="9">
         <v>23300</v>
       </c>
-      <c r="M45" s="9">
+      <c r="N45" s="9">
         <v>22900</v>
       </c>
-      <c r="N45" s="7">
+      <c r="O45" s="7">
         <v>74500</v>
       </c>
-      <c r="O45" s="7">
+      <c r="P45" s="7">
         <v>68500</v>
       </c>
-      <c r="P45" s="7">
+      <c r="Q45" s="7">
         <v>67200</v>
       </c>
-      <c r="Q45" s="7">
+      <c r="R45" s="7">
         <v>59100</v>
       </c>
-      <c r="R45" s="7">
+      <c r="S45" s="7">
         <v>60700</v>
       </c>
-      <c r="S45" s="7">
+      <c r="T45" s="7">
         <v>55000</v>
       </c>
-      <c r="T45" s="7">
+      <c r="U45" s="7">
         <v>53400</v>
       </c>
-      <c r="U45" s="7">
+      <c r="V45" s="7">
         <v>46100</v>
       </c>
-      <c r="V45" s="4">
+      <c r="W45" s="4">
         <v>51000</v>
       </c>
-      <c r="W45" s="4">
+      <c r="X45" s="4">
         <v>42800</v>
       </c>
-      <c r="X45" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y45" s="4" t="s">
         <v>8</v>
       </c>
@@ -3550,74 +3649,77 @@
       <c r="AC45" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD45" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="9">
+        <v>901900</v>
+      </c>
+      <c r="E46" s="9">
         <v>1006800</v>
       </c>
-      <c r="E46" s="9">
+      <c r="F46" s="9">
         <v>1097200</v>
       </c>
-      <c r="F46" s="9">
+      <c r="G46" s="9">
         <v>1021300</v>
       </c>
-      <c r="G46" s="9">
+      <c r="H46" s="9">
         <v>1136500</v>
       </c>
-      <c r="H46" s="9">
+      <c r="I46" s="9">
         <v>1196100</v>
       </c>
-      <c r="I46" s="9">
+      <c r="J46" s="9">
         <v>1265400</v>
       </c>
-      <c r="J46" s="9">
+      <c r="K46" s="9">
         <v>1232800</v>
       </c>
-      <c r="K46" s="9">
+      <c r="L46" s="9">
         <v>1197000</v>
       </c>
-      <c r="L46" s="9">
+      <c r="M46" s="9">
         <v>1367100</v>
       </c>
-      <c r="M46" s="9">
+      <c r="N46" s="9">
         <v>1355500</v>
       </c>
-      <c r="N46" s="7">
+      <c r="O46" s="7">
         <v>1319500</v>
       </c>
-      <c r="O46" s="7">
+      <c r="P46" s="7">
         <v>1303300</v>
       </c>
-      <c r="P46" s="7">
+      <c r="Q46" s="7">
         <v>1290700</v>
       </c>
-      <c r="Q46" s="7">
+      <c r="R46" s="7">
         <v>1277000</v>
       </c>
-      <c r="R46" s="7">
+      <c r="S46" s="7">
         <v>1269100</v>
       </c>
-      <c r="S46" s="7">
+      <c r="T46" s="7">
         <v>1284600</v>
       </c>
-      <c r="T46" s="7">
+      <c r="U46" s="7">
         <v>1299700</v>
       </c>
-      <c r="U46" s="7">
+      <c r="V46" s="7">
         <v>1421400</v>
       </c>
-      <c r="V46" s="4">
+      <c r="W46" s="4">
         <v>1421800</v>
       </c>
-      <c r="W46" s="4">
+      <c r="X46" s="4">
         <v>323800</v>
       </c>
-      <c r="X46" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y46" s="4" t="s">
         <v>8</v>
       </c>
@@ -3633,8 +3735,11 @@
       <c r="AC46" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD46" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3668,8 +3773,8 @@
       <c r="M47" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="7">
-        <v>0</v>
+      <c r="N47" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="7">
         <v>0</v>
@@ -3692,7 +3797,7 @@
       <c r="U47" s="7">
         <v>0</v>
       </c>
-      <c r="V47" s="4">
+      <c r="V47" s="7">
         <v>0</v>
       </c>
       <c r="W47" s="4">
@@ -3716,74 +3821,77 @@
       <c r="AC47" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD47" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="9">
+        <v>51800</v>
+      </c>
+      <c r="E48" s="9">
         <v>53600</v>
       </c>
-      <c r="E48" s="9">
+      <c r="F48" s="9">
         <v>52600</v>
       </c>
-      <c r="F48" s="9">
+      <c r="G48" s="9">
         <v>48600</v>
       </c>
-      <c r="G48" s="9">
+      <c r="H48" s="9">
         <v>42900</v>
       </c>
-      <c r="H48" s="9">
+      <c r="I48" s="9">
         <v>47300</v>
       </c>
-      <c r="I48" s="9">
+      <c r="J48" s="9">
         <v>48300</v>
       </c>
-      <c r="J48" s="9">
+      <c r="K48" s="9">
         <v>41400</v>
       </c>
-      <c r="K48" s="9">
+      <c r="L48" s="9">
         <v>41600</v>
       </c>
-      <c r="L48" s="9">
+      <c r="M48" s="9">
         <v>38500</v>
       </c>
-      <c r="M48" s="9">
+      <c r="N48" s="9">
         <v>41400</v>
       </c>
-      <c r="N48" s="7">
+      <c r="O48" s="7">
         <v>55200</v>
       </c>
-      <c r="O48" s="7">
+      <c r="P48" s="7">
         <v>52800</v>
       </c>
-      <c r="P48" s="7">
+      <c r="Q48" s="7">
         <v>55400</v>
       </c>
-      <c r="Q48" s="7">
+      <c r="R48" s="7">
         <v>57200</v>
       </c>
-      <c r="R48" s="7">
+      <c r="S48" s="7">
         <v>52200</v>
       </c>
-      <c r="S48" s="7">
+      <c r="T48" s="7">
         <v>52000</v>
       </c>
-      <c r="T48" s="7">
+      <c r="U48" s="7">
         <v>49300</v>
       </c>
-      <c r="U48" s="7">
+      <c r="V48" s="7">
         <v>21500</v>
       </c>
-      <c r="V48" s="4">
+      <c r="W48" s="4">
         <v>21200</v>
       </c>
-      <c r="W48" s="4">
+      <c r="X48" s="4">
         <v>21400</v>
       </c>
-      <c r="X48" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y48" s="4" t="s">
         <v>8</v>
       </c>
@@ -3799,43 +3907,46 @@
       <c r="AC48" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD48" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="9">
+        <v>317400</v>
+      </c>
+      <c r="E49" s="9">
         <v>323600</v>
       </c>
-      <c r="E49" s="9">
+      <c r="F49" s="9">
         <v>249800</v>
       </c>
-      <c r="F49" s="9">
+      <c r="G49" s="9">
         <v>250700</v>
       </c>
-      <c r="G49" s="9">
+      <c r="H49" s="9">
         <v>250900</v>
       </c>
-      <c r="H49" s="9">
+      <c r="I49" s="9">
         <v>250600</v>
       </c>
-      <c r="I49" s="9">
+      <c r="J49" s="9">
         <v>252400</v>
       </c>
-      <c r="J49" s="9">
+      <c r="K49" s="9">
         <v>256000</v>
       </c>
-      <c r="K49" s="9">
+      <c r="L49" s="9">
         <v>259500</v>
       </c>
-      <c r="L49" s="9">
+      <c r="M49" s="9">
         <v>20500</v>
       </c>
-      <c r="M49" s="9">
+      <c r="N49" s="9">
         <v>20300</v>
-      </c>
-      <c r="N49" s="7">
-        <v>6200</v>
       </c>
       <c r="O49" s="7">
         <v>6200</v>
@@ -3844,29 +3955,29 @@
         <v>6200</v>
       </c>
       <c r="Q49" s="7">
+        <v>6200</v>
+      </c>
+      <c r="R49" s="7">
         <v>6500</v>
       </c>
-      <c r="R49" s="7">
+      <c r="S49" s="7">
         <v>6800</v>
       </c>
-      <c r="S49" s="7">
+      <c r="T49" s="7">
         <v>7000</v>
       </c>
-      <c r="T49" s="7">
+      <c r="U49" s="7">
         <v>7500</v>
       </c>
-      <c r="U49" s="7">
+      <c r="V49" s="7">
         <v>8100</v>
       </c>
-      <c r="V49" s="4">
+      <c r="W49" s="4">
         <v>9200</v>
       </c>
-      <c r="W49" s="4">
+      <c r="X49" s="4">
         <v>10300</v>
       </c>
-      <c r="X49" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y49" s="4" t="s">
         <v>8</v>
       </c>
@@ -3882,8 +3993,11 @@
       <c r="AC49" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD49" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3917,7 +4031,7 @@
       <c r="M50" s="9">
         <v>0</v>
       </c>
-      <c r="N50" s="7">
+      <c r="N50" s="9">
         <v>0</v>
       </c>
       <c r="O50" s="7">
@@ -3941,7 +4055,7 @@
       <c r="U50" s="7">
         <v>0</v>
       </c>
-      <c r="V50" s="4">
+      <c r="V50" s="7">
         <v>0</v>
       </c>
       <c r="W50" s="4">
@@ -3965,8 +4079,11 @@
       <c r="AC50" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD50" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4000,7 +4117,7 @@
       <c r="M51" s="9">
         <v>0</v>
       </c>
-      <c r="N51" s="7">
+      <c r="N51" s="9">
         <v>0</v>
       </c>
       <c r="O51" s="7">
@@ -4024,7 +4141,7 @@
       <c r="U51" s="7">
         <v>0</v>
       </c>
-      <c r="V51" s="4">
+      <c r="V51" s="7">
         <v>0</v>
       </c>
       <c r="W51" s="4">
@@ -4048,74 +4165,77 @@
       <c r="AC51" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD51" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="9">
+        <v>16700</v>
+      </c>
+      <c r="E52" s="9">
         <v>17600</v>
       </c>
-      <c r="E52" s="9">
+      <c r="F52" s="9">
         <v>18500</v>
       </c>
-      <c r="F52" s="9">
+      <c r="G52" s="9">
         <v>16600</v>
       </c>
-      <c r="G52" s="9">
+      <c r="H52" s="9">
         <v>17100</v>
       </c>
-      <c r="H52" s="9">
+      <c r="I52" s="9">
         <v>15000</v>
       </c>
-      <c r="I52" s="9">
+      <c r="J52" s="9">
         <v>14800</v>
       </c>
-      <c r="J52" s="9">
+      <c r="K52" s="9">
         <v>13800</v>
       </c>
-      <c r="K52" s="9">
+      <c r="L52" s="9">
         <v>14400</v>
       </c>
-      <c r="L52" s="9">
+      <c r="M52" s="9">
         <v>12000</v>
       </c>
-      <c r="M52" s="9">
+      <c r="N52" s="9">
         <v>9800</v>
       </c>
-      <c r="N52" s="7">
+      <c r="O52" s="7">
         <v>37200</v>
       </c>
-      <c r="O52" s="7">
+      <c r="P52" s="7">
         <v>38100</v>
       </c>
-      <c r="P52" s="7">
+      <c r="Q52" s="7">
         <v>38600</v>
       </c>
-      <c r="Q52" s="7">
+      <c r="R52" s="7">
         <v>39600</v>
       </c>
-      <c r="R52" s="7">
+      <c r="S52" s="7">
         <v>35000</v>
       </c>
-      <c r="S52" s="7">
+      <c r="T52" s="7">
         <v>34700</v>
       </c>
-      <c r="T52" s="7">
+      <c r="U52" s="7">
         <v>34200</v>
       </c>
-      <c r="U52" s="7">
+      <c r="V52" s="7">
         <v>31900</v>
       </c>
-      <c r="V52" s="4">
+      <c r="W52" s="4">
         <v>35300</v>
       </c>
-      <c r="W52" s="4">
+      <c r="X52" s="4">
         <v>24400</v>
       </c>
-      <c r="X52" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y52" s="4" t="s">
         <v>8</v>
       </c>
@@ -4131,8 +4251,11 @@
       <c r="AC52" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD52" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4166,7 +4289,7 @@
       <c r="M53" s="9">
         <v>0</v>
       </c>
-      <c r="N53" s="7">
+      <c r="N53" s="9">
         <v>0</v>
       </c>
       <c r="O53" s="7">
@@ -4190,7 +4313,7 @@
       <c r="U53" s="7">
         <v>0</v>
       </c>
-      <c r="V53" s="4">
+      <c r="V53" s="7">
         <v>0</v>
       </c>
       <c r="W53" s="4">
@@ -4214,74 +4337,77 @@
       <c r="AC53" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD53" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="9">
+        <v>1490500</v>
+      </c>
+      <c r="E54" s="9">
         <v>1605400</v>
       </c>
-      <c r="E54" s="9">
+      <c r="F54" s="9">
         <v>1602700</v>
       </c>
-      <c r="F54" s="9">
+      <c r="G54" s="9">
         <v>1372000</v>
       </c>
-      <c r="G54" s="9">
+      <c r="H54" s="9">
         <v>1480800</v>
       </c>
-      <c r="H54" s="9">
+      <c r="I54" s="9">
         <v>1541200</v>
       </c>
-      <c r="I54" s="9">
+      <c r="J54" s="9">
         <v>1611900</v>
       </c>
-      <c r="J54" s="9">
+      <c r="K54" s="9">
         <v>1575200</v>
       </c>
-      <c r="K54" s="9">
+      <c r="L54" s="9">
         <v>1543600</v>
       </c>
-      <c r="L54" s="9">
+      <c r="M54" s="9">
         <v>1467400</v>
       </c>
-      <c r="M54" s="9">
+      <c r="N54" s="9">
         <v>1456800</v>
       </c>
-      <c r="N54" s="7">
+      <c r="O54" s="7">
         <v>1418100</v>
       </c>
-      <c r="O54" s="7">
+      <c r="P54" s="7">
         <v>1400300</v>
       </c>
-      <c r="P54" s="7">
+      <c r="Q54" s="7">
         <v>1390800</v>
       </c>
-      <c r="Q54" s="7">
+      <c r="R54" s="7">
         <v>1380200</v>
       </c>
-      <c r="R54" s="7">
+      <c r="S54" s="7">
         <v>1363100</v>
       </c>
-      <c r="S54" s="7">
+      <c r="T54" s="7">
         <v>1378300</v>
       </c>
-      <c r="T54" s="7">
+      <c r="U54" s="7">
         <v>1390700</v>
       </c>
-      <c r="U54" s="7">
+      <c r="V54" s="7">
         <v>1482800</v>
       </c>
-      <c r="V54" s="4">
+      <c r="W54" s="4">
         <v>1487500</v>
       </c>
-      <c r="W54" s="4">
+      <c r="X54" s="4">
         <v>379800</v>
       </c>
-      <c r="X54" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y54" s="4" t="s">
         <v>8</v>
       </c>
@@ -4297,8 +4423,11 @@
       <c r="AC54" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD54" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4312,7 +4441,7 @@
       <c r="K55" s="9"/>
       <c r="L55" s="9"/>
       <c r="M55" s="9"/>
-      <c r="N55" s="7"/>
+      <c r="N55" s="9"/>
       <c r="O55" s="7"/>
       <c r="P55" s="7"/>
       <c r="Q55" s="7"/>
@@ -4320,7 +4449,7 @@
       <c r="S55" s="7"/>
       <c r="T55" s="7"/>
       <c r="U55" s="7"/>
-      <c r="V55" s="4"/>
+      <c r="V55" s="7"/>
       <c r="W55" s="4"/>
       <c r="X55" s="4"/>
       <c r="Y55" s="4"/>
@@ -4328,8 +4457,9 @@
       <c r="AA55" s="4"/>
       <c r="AB55" s="4"/>
       <c r="AC55" s="4"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD55" s="4"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4343,7 +4473,7 @@
       <c r="K56" s="9"/>
       <c r="L56" s="9"/>
       <c r="M56" s="9"/>
-      <c r="N56" s="7"/>
+      <c r="N56" s="9"/>
       <c r="O56" s="7"/>
       <c r="P56" s="7"/>
       <c r="Q56" s="7"/>
@@ -4351,7 +4481,7 @@
       <c r="S56" s="7"/>
       <c r="T56" s="7"/>
       <c r="U56" s="7"/>
-      <c r="V56" s="4"/>
+      <c r="V56" s="7"/>
       <c r="W56" s="4"/>
       <c r="X56" s="4"/>
       <c r="Y56" s="4"/>
@@ -4359,74 +4489,75 @@
       <c r="AA56" s="4"/>
       <c r="AB56" s="4"/>
       <c r="AC56" s="4"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD56" s="4"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="9">
+        <v>26900</v>
+      </c>
+      <c r="E57" s="9">
         <v>18600</v>
       </c>
-      <c r="E57" s="9">
+      <c r="F57" s="9">
         <v>11500</v>
       </c>
-      <c r="F57" s="9">
+      <c r="G57" s="9">
         <v>7600</v>
       </c>
-      <c r="G57" s="9">
+      <c r="H57" s="9">
         <v>4900</v>
       </c>
-      <c r="H57" s="9">
+      <c r="I57" s="9">
         <v>2100</v>
       </c>
-      <c r="I57" s="9">
+      <c r="J57" s="9">
         <v>1600</v>
       </c>
-      <c r="J57" s="9">
+      <c r="K57" s="9">
         <v>7000</v>
       </c>
-      <c r="K57" s="9">
+      <c r="L57" s="9">
         <v>9800</v>
       </c>
-      <c r="L57" s="9">
+      <c r="M57" s="9">
         <v>1500</v>
       </c>
-      <c r="M57" s="9">
+      <c r="N57" s="9">
         <v>3500</v>
       </c>
-      <c r="N57" s="7">
+      <c r="O57" s="7">
         <v>2700</v>
       </c>
-      <c r="O57" s="7">
+      <c r="P57" s="7">
         <v>1700</v>
       </c>
-      <c r="P57" s="7">
+      <c r="Q57" s="7">
         <v>4400</v>
       </c>
-      <c r="Q57" s="7">
+      <c r="R57" s="7">
         <v>5900</v>
       </c>
-      <c r="R57" s="7">
+      <c r="S57" s="7">
         <v>3900</v>
       </c>
-      <c r="S57" s="7">
+      <c r="T57" s="7">
         <v>6300</v>
       </c>
-      <c r="T57" s="7">
+      <c r="U57" s="7">
         <v>3800</v>
       </c>
-      <c r="U57" s="7">
+      <c r="V57" s="7">
         <v>6300</v>
       </c>
-      <c r="V57" s="4">
+      <c r="W57" s="4">
         <v>3200</v>
       </c>
-      <c r="W57" s="4">
+      <c r="X57" s="4">
         <v>8100</v>
       </c>
-      <c r="X57" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y57" s="4" t="s">
         <v>8</v>
       </c>
@@ -4442,44 +4573,47 @@
       <c r="AC57" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD57" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="9">
+        <v>9000</v>
+      </c>
+      <c r="E58" s="9">
         <v>9400</v>
       </c>
-      <c r="E58" s="9">
+      <c r="F58" s="9">
         <v>9200</v>
       </c>
-      <c r="F58" s="9">
+      <c r="G58" s="9">
         <v>8200</v>
       </c>
-      <c r="G58" s="9">
+      <c r="H58" s="9">
         <v>9200</v>
       </c>
-      <c r="H58" s="9">
+      <c r="I58" s="9">
         <v>9300</v>
       </c>
-      <c r="I58" s="9">
+      <c r="J58" s="9">
         <v>8100</v>
       </c>
-      <c r="J58" s="9">
+      <c r="K58" s="9">
         <v>5600</v>
       </c>
-      <c r="K58" s="9">
+      <c r="L58" s="9">
         <v>4000</v>
       </c>
-      <c r="L58" s="9">
+      <c r="M58" s="9">
         <v>1700</v>
       </c>
-      <c r="M58" s="9">
+      <c r="N58" s="9">
         <v>2700</v>
       </c>
-      <c r="N58" s="7">
-        <v>0</v>
-      </c>
       <c r="O58" s="7">
         <v>0</v>
       </c>
@@ -4501,7 +4635,7 @@
       <c r="U58" s="7">
         <v>0</v>
       </c>
-      <c r="V58" s="4">
+      <c r="V58" s="7">
         <v>0</v>
       </c>
       <c r="W58" s="4">
@@ -4525,74 +4659,77 @@
       <c r="AC58" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="9">
+        <v>420900</v>
+      </c>
+      <c r="E59" s="9">
         <v>416200</v>
       </c>
-      <c r="E59" s="9">
+      <c r="F59" s="9">
         <v>402100</v>
       </c>
-      <c r="F59" s="9">
+      <c r="G59" s="9">
         <v>363300</v>
       </c>
-      <c r="G59" s="9">
+      <c r="H59" s="9">
         <v>351200</v>
       </c>
-      <c r="H59" s="9">
+      <c r="I59" s="9">
         <v>339300</v>
       </c>
-      <c r="I59" s="9">
+      <c r="J59" s="9">
         <v>331600</v>
       </c>
-      <c r="J59" s="9">
+      <c r="K59" s="9">
         <v>305400</v>
       </c>
-      <c r="K59" s="9">
+      <c r="L59" s="9">
         <v>294800</v>
       </c>
-      <c r="L59" s="9">
+      <c r="M59" s="9">
         <v>284700</v>
       </c>
-      <c r="M59" s="9">
+      <c r="N59" s="9">
         <v>272700</v>
       </c>
-      <c r="N59" s="7">
+      <c r="O59" s="7">
         <v>303000</v>
       </c>
-      <c r="O59" s="7">
+      <c r="P59" s="7">
         <v>289900</v>
       </c>
-      <c r="P59" s="7">
+      <c r="Q59" s="7">
         <v>281100</v>
       </c>
-      <c r="Q59" s="7">
+      <c r="R59" s="7">
         <v>265800</v>
       </c>
-      <c r="R59" s="7">
+      <c r="S59" s="7">
         <v>248500</v>
       </c>
-      <c r="S59" s="7">
+      <c r="T59" s="7">
         <v>242000</v>
       </c>
-      <c r="T59" s="7">
+      <c r="U59" s="7">
         <v>227900</v>
       </c>
-      <c r="U59" s="7">
+      <c r="V59" s="7">
         <v>217000</v>
       </c>
-      <c r="V59" s="4">
+      <c r="W59" s="4">
         <v>198200</v>
       </c>
-      <c r="W59" s="4">
+      <c r="X59" s="4">
         <v>164600</v>
       </c>
-      <c r="X59" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y59" s="4" t="s">
         <v>8</v>
       </c>
@@ -4608,74 +4745,77 @@
       <c r="AC59" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD59" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="9">
+        <v>532700</v>
+      </c>
+      <c r="E60" s="9">
         <v>520100</v>
       </c>
-      <c r="E60" s="9">
+      <c r="F60" s="9">
         <v>498000</v>
       </c>
-      <c r="F60" s="9">
+      <c r="G60" s="9">
         <v>450600</v>
       </c>
-      <c r="G60" s="9">
+      <c r="H60" s="9">
         <v>432600</v>
       </c>
-      <c r="H60" s="9">
+      <c r="I60" s="9">
         <v>413500</v>
       </c>
-      <c r="I60" s="9">
+      <c r="J60" s="9">
         <v>407700</v>
       </c>
-      <c r="J60" s="9">
+      <c r="K60" s="9">
         <v>377900</v>
       </c>
-      <c r="K60" s="9">
+      <c r="L60" s="9">
         <v>367700</v>
       </c>
-      <c r="L60" s="9">
+      <c r="M60" s="9">
         <v>336300</v>
       </c>
-      <c r="M60" s="9">
+      <c r="N60" s="9">
         <v>327200</v>
       </c>
-      <c r="N60" s="7">
+      <c r="O60" s="7">
         <v>305700</v>
       </c>
-      <c r="O60" s="7">
+      <c r="P60" s="7">
         <v>291600</v>
       </c>
-      <c r="P60" s="7">
+      <c r="Q60" s="7">
         <v>285500</v>
       </c>
-      <c r="Q60" s="7">
+      <c r="R60" s="7">
         <v>271700</v>
       </c>
-      <c r="R60" s="7">
+      <c r="S60" s="7">
         <v>252400</v>
       </c>
-      <c r="S60" s="7">
+      <c r="T60" s="7">
         <v>248300</v>
       </c>
-      <c r="T60" s="7">
+      <c r="U60" s="7">
         <v>231700</v>
       </c>
-      <c r="U60" s="7">
+      <c r="V60" s="7">
         <v>223300</v>
       </c>
-      <c r="V60" s="4">
+      <c r="W60" s="4">
         <v>201400</v>
       </c>
-      <c r="W60" s="4">
+      <c r="X60" s="4">
         <v>172800</v>
       </c>
-      <c r="X60" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y60" s="4" t="s">
         <v>8</v>
       </c>
@@ -4691,44 +4831,47 @@
       <c r="AC60" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD60" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="9">
+        <v>25600</v>
+      </c>
+      <c r="E61" s="9">
         <v>29400</v>
       </c>
-      <c r="E61" s="9">
+      <c r="F61" s="9">
         <v>33300</v>
       </c>
-      <c r="F61" s="9">
+      <c r="G61" s="9">
         <v>31400</v>
       </c>
-      <c r="G61" s="9">
+      <c r="H61" s="9">
         <v>26800</v>
       </c>
-      <c r="H61" s="9">
+      <c r="I61" s="9">
         <v>30600</v>
       </c>
-      <c r="I61" s="9">
+      <c r="J61" s="9">
         <v>30200</v>
       </c>
-      <c r="J61" s="9">
+      <c r="K61" s="9">
         <v>25500</v>
       </c>
-      <c r="K61" s="9">
+      <c r="L61" s="9">
         <v>27700</v>
       </c>
-      <c r="L61" s="9">
+      <c r="M61" s="9">
         <v>24600</v>
       </c>
-      <c r="M61" s="9">
+      <c r="N61" s="9">
         <v>26800</v>
       </c>
-      <c r="N61" s="7">
-        <v>0</v>
-      </c>
       <c r="O61" s="7">
         <v>0</v>
       </c>
@@ -4750,7 +4893,7 @@
       <c r="U61" s="7">
         <v>0</v>
       </c>
-      <c r="V61" s="4">
+      <c r="V61" s="7">
         <v>0</v>
       </c>
       <c r="W61" s="4">
@@ -4774,74 +4917,77 @@
       <c r="AC61" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD61" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="9">
+        <v>33400</v>
+      </c>
+      <c r="E62" s="9">
         <v>33800</v>
       </c>
-      <c r="E62" s="9">
+      <c r="F62" s="9">
         <v>24800</v>
       </c>
-      <c r="F62" s="9">
+      <c r="G62" s="9">
         <v>34800</v>
       </c>
-      <c r="G62" s="9">
+      <c r="H62" s="9">
         <v>33300</v>
       </c>
-      <c r="H62" s="9">
+      <c r="I62" s="9">
         <v>31500</v>
       </c>
-      <c r="I62" s="9">
+      <c r="J62" s="9">
         <v>22500</v>
       </c>
-      <c r="J62" s="9">
+      <c r="K62" s="9">
         <v>33400</v>
       </c>
-      <c r="K62" s="9">
+      <c r="L62" s="9">
         <v>33100</v>
       </c>
-      <c r="L62" s="9">
+      <c r="M62" s="9">
         <v>28400</v>
       </c>
-      <c r="M62" s="9">
+      <c r="N62" s="9">
         <v>20000</v>
       </c>
-      <c r="N62" s="7">
+      <c r="O62" s="7">
         <v>53900</v>
       </c>
-      <c r="O62" s="7">
+      <c r="P62" s="7">
         <v>51100</v>
       </c>
-      <c r="P62" s="7">
+      <c r="Q62" s="7">
         <v>54900</v>
       </c>
-      <c r="Q62" s="7">
+      <c r="R62" s="7">
         <v>56700</v>
       </c>
-      <c r="R62" s="7">
+      <c r="S62" s="7">
         <v>50700</v>
       </c>
-      <c r="S62" s="7">
+      <c r="T62" s="7">
         <v>50300</v>
       </c>
-      <c r="T62" s="7">
+      <c r="U62" s="7">
         <v>47800</v>
       </c>
-      <c r="U62" s="7">
+      <c r="V62" s="7">
         <v>21400</v>
       </c>
-      <c r="V62" s="4">
+      <c r="W62" s="4">
         <v>18300</v>
       </c>
-      <c r="W62" s="4">
+      <c r="X62" s="4">
         <v>18900</v>
       </c>
-      <c r="X62" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y62" s="4" t="s">
         <v>8</v>
       </c>
@@ -4857,8 +5003,11 @@
       <c r="AC62" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD62" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4892,7 +5041,7 @@
       <c r="M63" s="9">
         <v>0</v>
       </c>
-      <c r="N63" s="7">
+      <c r="N63" s="9">
         <v>0</v>
       </c>
       <c r="O63" s="7">
@@ -4916,7 +5065,7 @@
       <c r="U63" s="7">
         <v>0</v>
       </c>
-      <c r="V63" s="4">
+      <c r="V63" s="7">
         <v>0</v>
       </c>
       <c r="W63" s="4">
@@ -4940,8 +5089,11 @@
       <c r="AC63" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD63" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4975,7 +5127,7 @@
       <c r="M64" s="9">
         <v>0</v>
       </c>
-      <c r="N64" s="7">
+      <c r="N64" s="9">
         <v>0</v>
       </c>
       <c r="O64" s="7">
@@ -4999,7 +5151,7 @@
       <c r="U64" s="7">
         <v>0</v>
       </c>
-      <c r="V64" s="4">
+      <c r="V64" s="7">
         <v>0</v>
       </c>
       <c r="W64" s="4">
@@ -5023,8 +5175,11 @@
       <c r="AC64" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD64" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5058,7 +5213,7 @@
       <c r="M65" s="9">
         <v>0</v>
       </c>
-      <c r="N65" s="7">
+      <c r="N65" s="9">
         <v>0</v>
       </c>
       <c r="O65" s="7">
@@ -5082,7 +5237,7 @@
       <c r="U65" s="7">
         <v>0</v>
       </c>
-      <c r="V65" s="4">
+      <c r="V65" s="7">
         <v>0</v>
       </c>
       <c r="W65" s="4">
@@ -5106,74 +5261,77 @@
       <c r="AC65" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD65" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="9">
+        <v>594500</v>
+      </c>
+      <c r="E66" s="9">
         <v>586200</v>
       </c>
-      <c r="E66" s="9">
+      <c r="F66" s="9">
         <v>570100</v>
       </c>
-      <c r="F66" s="9">
+      <c r="G66" s="9">
         <v>520500</v>
       </c>
-      <c r="G66" s="9">
+      <c r="H66" s="9">
         <v>496200</v>
       </c>
-      <c r="H66" s="9">
+      <c r="I66" s="9">
         <v>479400</v>
       </c>
-      <c r="I66" s="9">
+      <c r="J66" s="9">
         <v>474000</v>
       </c>
-      <c r="J66" s="9">
+      <c r="K66" s="9">
         <v>440200</v>
       </c>
-      <c r="K66" s="9">
+      <c r="L66" s="9">
         <v>428500</v>
       </c>
-      <c r="L66" s="9">
+      <c r="M66" s="9">
         <v>389300</v>
       </c>
-      <c r="M66" s="9">
+      <c r="N66" s="9">
         <v>384500</v>
       </c>
-      <c r="N66" s="7">
+      <c r="O66" s="7">
         <v>359600</v>
       </c>
-      <c r="O66" s="7">
+      <c r="P66" s="7">
         <v>342700</v>
       </c>
-      <c r="P66" s="7">
+      <c r="Q66" s="7">
         <v>340400</v>
       </c>
-      <c r="Q66" s="7">
+      <c r="R66" s="7">
         <v>328400</v>
       </c>
-      <c r="R66" s="7">
+      <c r="S66" s="7">
         <v>303100</v>
       </c>
-      <c r="S66" s="7">
+      <c r="T66" s="7">
         <v>298700</v>
       </c>
-      <c r="T66" s="7">
+      <c r="U66" s="7">
         <v>279500</v>
       </c>
-      <c r="U66" s="7">
+      <c r="V66" s="7">
         <v>244800</v>
       </c>
-      <c r="V66" s="4">
+      <c r="W66" s="4">
         <v>219600</v>
       </c>
-      <c r="W66" s="4">
+      <c r="X66" s="4">
         <v>191700</v>
       </c>
-      <c r="X66" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y66" s="4" t="s">
         <v>8</v>
       </c>
@@ -5189,8 +5347,11 @@
       <c r="AC66" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD66" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5204,7 +5365,7 @@
       <c r="K67" s="9"/>
       <c r="L67" s="9"/>
       <c r="M67" s="9"/>
-      <c r="N67" s="7"/>
+      <c r="N67" s="9"/>
       <c r="O67" s="7"/>
       <c r="P67" s="7"/>
       <c r="Q67" s="7"/>
@@ -5212,7 +5373,7 @@
       <c r="S67" s="7"/>
       <c r="T67" s="7"/>
       <c r="U67" s="7"/>
-      <c r="V67" s="4"/>
+      <c r="V67" s="7"/>
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
       <c r="Y67" s="4"/>
@@ -5220,8 +5381,9 @@
       <c r="AA67" s="4"/>
       <c r="AB67" s="4"/>
       <c r="AC67" s="4"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD67" s="4"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5255,7 +5417,7 @@
       <c r="M68" s="9">
         <v>0</v>
       </c>
-      <c r="N68" s="7">
+      <c r="N68" s="9">
         <v>0</v>
       </c>
       <c r="O68" s="7">
@@ -5279,7 +5441,7 @@
       <c r="U68" s="7">
         <v>0</v>
       </c>
-      <c r="V68" s="4">
+      <c r="V68" s="7">
         <v>0</v>
       </c>
       <c r="W68" s="4">
@@ -5303,8 +5465,11 @@
       <c r="AC68" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD68" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5338,7 +5503,7 @@
       <c r="M69" s="9">
         <v>0</v>
       </c>
-      <c r="N69" s="7">
+      <c r="N69" s="9">
         <v>0</v>
       </c>
       <c r="O69" s="7">
@@ -5362,7 +5527,7 @@
       <c r="U69" s="7">
         <v>0</v>
       </c>
-      <c r="V69" s="4">
+      <c r="V69" s="7">
         <v>0</v>
       </c>
       <c r="W69" s="4">
@@ -5386,8 +5551,11 @@
       <c r="AC69" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD69" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5421,7 +5589,7 @@
       <c r="M70" s="9">
         <v>0</v>
       </c>
-      <c r="N70" s="7">
+      <c r="N70" s="9">
         <v>0</v>
       </c>
       <c r="O70" s="7">
@@ -5445,15 +5613,15 @@
       <c r="U70" s="7">
         <v>0</v>
       </c>
-      <c r="V70" s="4">
+      <c r="V70" s="7">
         <v>0</v>
       </c>
       <c r="W70" s="4">
+        <v>0</v>
+      </c>
+      <c r="X70" s="4">
         <v>3276900</v>
       </c>
-      <c r="X70" s="4">
-        <v>0</v>
-      </c>
       <c r="Y70" s="4">
         <v>0</v>
       </c>
@@ -5469,8 +5637,11 @@
       <c r="AC70" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD70" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5504,7 +5675,7 @@
       <c r="M71" s="9">
         <v>0</v>
       </c>
-      <c r="N71" s="7">
+      <c r="N71" s="9">
         <v>0</v>
       </c>
       <c r="O71" s="7">
@@ -5528,7 +5699,7 @@
       <c r="U71" s="7">
         <v>0</v>
       </c>
-      <c r="V71" s="4">
+      <c r="V71" s="7">
         <v>0</v>
       </c>
       <c r="W71" s="4">
@@ -5552,74 +5723,77 @@
       <c r="AC71" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD71" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="9">
+        <v>-3553700</v>
+      </c>
+      <c r="E72" s="9">
         <v>-3557000</v>
       </c>
-      <c r="E72" s="9">
+      <c r="F72" s="9">
         <v>-3552200</v>
       </c>
-      <c r="F72" s="9">
+      <c r="G72" s="9">
         <v>-3743600</v>
       </c>
-      <c r="G72" s="9">
+      <c r="H72" s="9">
         <v>-3738900</v>
       </c>
-      <c r="H72" s="9">
+      <c r="I72" s="9">
         <v>-3737200</v>
       </c>
-      <c r="I72" s="9">
+      <c r="J72" s="9">
         <v>-3735900</v>
       </c>
-      <c r="J72" s="9">
+      <c r="K72" s="9">
         <v>-3714000</v>
       </c>
-      <c r="K72" s="9">
+      <c r="L72" s="9">
         <v>-3684000</v>
       </c>
-      <c r="L72" s="9">
+      <c r="M72" s="9">
         <v>-3663800</v>
       </c>
-      <c r="M72" s="9">
+      <c r="N72" s="9">
         <v>-3640500</v>
       </c>
-      <c r="N72" s="7">
+      <c r="O72" s="7">
         <v>-3612400</v>
       </c>
-      <c r="O72" s="7">
+      <c r="P72" s="7">
         <v>-3581400</v>
       </c>
-      <c r="P72" s="7">
+      <c r="Q72" s="7">
         <v>-3545700</v>
       </c>
-      <c r="Q72" s="7">
+      <c r="R72" s="7">
         <v>-3503100</v>
       </c>
-      <c r="R72" s="7">
+      <c r="S72" s="7">
         <v>-3447600</v>
       </c>
-      <c r="S72" s="7">
+      <c r="T72" s="7">
         <v>-3389800</v>
       </c>
-      <c r="T72" s="7">
+      <c r="U72" s="7">
         <v>-3320000</v>
       </c>
-      <c r="U72" s="7">
+      <c r="V72" s="7">
         <v>-3270900</v>
       </c>
-      <c r="V72" s="4">
+      <c r="W72" s="4">
         <v>-3196200</v>
       </c>
-      <c r="W72" s="4">
+      <c r="X72" s="4">
         <v>-3088800</v>
       </c>
-      <c r="X72" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y72" s="4" t="s">
         <v>8</v>
       </c>
@@ -5635,8 +5809,11 @@
       <c r="AC72" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD72" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5670,7 +5847,7 @@
       <c r="M73" s="9">
         <v>0</v>
       </c>
-      <c r="N73" s="7">
+      <c r="N73" s="9">
         <v>0</v>
       </c>
       <c r="O73" s="7">
@@ -5694,7 +5871,7 @@
       <c r="U73" s="7">
         <v>0</v>
       </c>
-      <c r="V73" s="4">
+      <c r="V73" s="7">
         <v>0</v>
       </c>
       <c r="W73" s="4">
@@ -5718,8 +5895,11 @@
       <c r="AC73" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD73" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5753,7 +5933,7 @@
       <c r="M74" s="9">
         <v>0</v>
       </c>
-      <c r="N74" s="7">
+      <c r="N74" s="9">
         <v>0</v>
       </c>
       <c r="O74" s="7">
@@ -5777,7 +5957,7 @@
       <c r="U74" s="7">
         <v>0</v>
       </c>
-      <c r="V74" s="4">
+      <c r="V74" s="7">
         <v>0</v>
       </c>
       <c r="W74" s="4">
@@ -5801,8 +5981,11 @@
       <c r="AC74" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD74" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5836,7 +6019,7 @@
       <c r="M75" s="9">
         <v>0</v>
       </c>
-      <c r="N75" s="7">
+      <c r="N75" s="9">
         <v>0</v>
       </c>
       <c r="O75" s="7">
@@ -5860,7 +6043,7 @@
       <c r="U75" s="7">
         <v>0</v>
       </c>
-      <c r="V75" s="4">
+      <c r="V75" s="7">
         <v>0</v>
       </c>
       <c r="W75" s="4">
@@ -5884,74 +6067,77 @@
       <c r="AC75" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD75" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="9">
+        <v>895900</v>
+      </c>
+      <c r="E76" s="9">
         <v>1019200</v>
       </c>
-      <c r="E76" s="9">
+      <c r="F76" s="9">
         <v>1032700</v>
       </c>
-      <c r="F76" s="9">
+      <c r="G76" s="9">
         <v>851500</v>
       </c>
-      <c r="G76" s="9">
+      <c r="H76" s="9">
         <v>984600</v>
       </c>
-      <c r="H76" s="9">
+      <c r="I76" s="9">
         <v>1061800</v>
       </c>
-      <c r="I76" s="9">
+      <c r="J76" s="9">
         <v>1137900</v>
       </c>
-      <c r="J76" s="9">
+      <c r="K76" s="9">
         <v>1135000</v>
       </c>
-      <c r="K76" s="9">
+      <c r="L76" s="9">
         <v>1115100</v>
       </c>
-      <c r="L76" s="9">
+      <c r="M76" s="9">
         <v>1078100</v>
       </c>
-      <c r="M76" s="9">
+      <c r="N76" s="9">
         <v>1072300</v>
       </c>
-      <c r="N76" s="7">
+      <c r="O76" s="7">
         <v>1058500</v>
       </c>
-      <c r="O76" s="7">
+      <c r="P76" s="7">
         <v>1057700</v>
       </c>
-      <c r="P76" s="7">
+      <c r="Q76" s="7">
         <v>1050400</v>
       </c>
-      <c r="Q76" s="7">
+      <c r="R76" s="7">
         <v>1051800</v>
       </c>
-      <c r="R76" s="7">
+      <c r="S76" s="7">
         <v>1060000</v>
       </c>
-      <c r="S76" s="7">
+      <c r="T76" s="7">
         <v>1079600</v>
       </c>
-      <c r="T76" s="7">
+      <c r="U76" s="7">
         <v>1111200</v>
       </c>
-      <c r="U76" s="7">
+      <c r="V76" s="7">
         <v>1238000</v>
       </c>
-      <c r="V76" s="4">
+      <c r="W76" s="4">
         <v>1267900</v>
       </c>
-      <c r="W76" s="4">
+      <c r="X76" s="4">
         <v>-3088800</v>
       </c>
-      <c r="X76" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="Y76" s="4" t="s">
         <v>8</v>
       </c>
@@ -5967,8 +6153,11 @@
       <c r="AC76" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD76" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6002,7 +6191,7 @@
       <c r="M77" s="9">
         <v>0</v>
       </c>
-      <c r="N77" s="7">
+      <c r="N77" s="9">
         <v>0</v>
       </c>
       <c r="O77" s="7">
@@ -6026,7 +6215,7 @@
       <c r="U77" s="7">
         <v>0</v>
       </c>
-      <c r="V77" s="4">
+      <c r="V77" s="7">
         <v>0</v>
       </c>
       <c r="W77" s="4">
@@ -6050,159 +6239,165 @@
       <c r="AC77" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="AD77" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="8">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="8">
         <v>46112</v>
       </c>
-      <c r="E80" s="8">
+      <c r="F80" s="8">
         <v>46022</v>
       </c>
-      <c r="F80" s="8">
+      <c r="G80" s="8">
         <v>45930</v>
       </c>
-      <c r="G80" s="8">
+      <c r="H80" s="8">
         <v>45838</v>
       </c>
-      <c r="H80" s="8">
+      <c r="I80" s="8">
         <v>45747</v>
       </c>
-      <c r="I80" s="8">
+      <c r="J80" s="8">
         <v>45657</v>
       </c>
-      <c r="J80" s="8">
+      <c r="K80" s="8">
         <v>45565</v>
       </c>
-      <c r="K80" s="8">
+      <c r="L80" s="8">
         <v>45473</v>
       </c>
-      <c r="L80" s="8">
+      <c r="M80" s="8">
         <v>45382</v>
       </c>
-      <c r="M80" s="8">
+      <c r="N80" s="8">
         <v>45291</v>
       </c>
-      <c r="N80" s="6">
+      <c r="O80" s="6">
         <v>45199</v>
       </c>
-      <c r="O80" s="6">
+      <c r="P80" s="6">
         <v>45107</v>
       </c>
-      <c r="P80" s="6">
+      <c r="Q80" s="6">
         <v>45016</v>
       </c>
-      <c r="Q80" s="6">
+      <c r="R80" s="6">
         <v>44926</v>
       </c>
-      <c r="R80" s="6">
+      <c r="S80" s="6">
         <v>44834</v>
       </c>
-      <c r="S80" s="6">
+      <c r="T80" s="6">
         <v>44742</v>
       </c>
-      <c r="T80" s="6">
+      <c r="U80" s="6">
         <v>44651</v>
       </c>
-      <c r="U80" s="6">
+      <c r="V80" s="6">
         <v>44561</v>
       </c>
-      <c r="V80" s="3">
+      <c r="W80" s="3">
         <v>44469</v>
       </c>
-      <c r="W80" s="3">
+      <c r="X80" s="3">
         <v>44377</v>
       </c>
-      <c r="X80" s="3">
+      <c r="Y80" s="3">
         <v>44286</v>
       </c>
-      <c r="Y80" s="3">
+      <c r="Z80" s="3">
         <v>44196</v>
       </c>
-      <c r="Z80" s="3">
+      <c r="AA80" s="3">
         <v>44104</v>
       </c>
-      <c r="AA80" s="3">
+      <c r="AB80" s="3">
         <v>44012</v>
       </c>
-      <c r="AB80" s="3">
+      <c r="AC80" s="3">
         <v>43921</v>
       </c>
-      <c r="AC80" s="3">
+      <c r="AD80" s="3">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="9">
+        <v>3200</v>
+      </c>
+      <c r="E81" s="9">
         <v>-4800</v>
       </c>
-      <c r="E81" s="9">
+      <c r="F81" s="9">
         <v>191400</v>
       </c>
-      <c r="F81" s="9">
+      <c r="G81" s="9">
         <v>-4700</v>
       </c>
-      <c r="G81" s="9">
+      <c r="H81" s="9">
         <v>-1700</v>
       </c>
-      <c r="H81" s="9">
+      <c r="I81" s="9">
         <v>-1300</v>
       </c>
-      <c r="I81" s="9">
+      <c r="J81" s="9">
         <v>-21900</v>
       </c>
-      <c r="J81" s="9">
+      <c r="K81" s="9">
         <v>-30000</v>
       </c>
-      <c r="K81" s="9">
+      <c r="L81" s="9">
         <v>-20200</v>
       </c>
-      <c r="L81" s="9">
+      <c r="M81" s="9">
         <v>-23300</v>
       </c>
-      <c r="M81" s="9">
+      <c r="N81" s="9">
         <v>-28100</v>
       </c>
-      <c r="N81" s="7">
+      <c r="O81" s="7">
         <v>-31000</v>
       </c>
-      <c r="O81" s="7">
+      <c r="P81" s="7">
         <v>-35700</v>
       </c>
-      <c r="P81" s="7">
+      <c r="Q81" s="7">
         <v>-42700</v>
       </c>
-      <c r="Q81" s="7">
+      <c r="R81" s="7">
         <v>-55500</v>
       </c>
-      <c r="R81" s="7">
+      <c r="S81" s="7">
         <v>-57800</v>
       </c>
-      <c r="S81" s="7">
+      <c r="T81" s="7">
         <v>-69800</v>
       </c>
-      <c r="T81" s="7">
+      <c r="U81" s="7">
         <v>-49100</v>
       </c>
-      <c r="U81" s="7">
+      <c r="V81" s="7">
         <v>-74700</v>
       </c>
-      <c r="V81" s="4">
+      <c r="W81" s="4">
         <v>-2372300</v>
       </c>
-      <c r="W81" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X81" s="4" t="s">
         <v>8</v>
       </c>
@@ -6221,8 +6416,11 @@
       <c r="AC81" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD81" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6236,7 +6434,7 @@
       <c r="K82" s="9"/>
       <c r="L82" s="9"/>
       <c r="M82" s="9"/>
-      <c r="N82" s="7"/>
+      <c r="N82" s="9"/>
       <c r="O82" s="7"/>
       <c r="P82" s="7"/>
       <c r="Q82" s="7"/>
@@ -6244,7 +6442,7 @@
       <c r="S82" s="7"/>
       <c r="T82" s="7"/>
       <c r="U82" s="7"/>
-      <c r="V82" s="4"/>
+      <c r="V82" s="7"/>
       <c r="W82" s="4"/>
       <c r="X82" s="4"/>
       <c r="Y82" s="4"/>
@@ -6252,16 +6450,17 @@
       <c r="AA82" s="4"/>
       <c r="AB82" s="4"/>
       <c r="AC82" s="4"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD82" s="4"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="9">
+        <v>1100</v>
+      </c>
+      <c r="E83" s="9">
         <v>1200</v>
-      </c>
-      <c r="E83" s="9">
-        <v>1300</v>
       </c>
       <c r="F83" s="9">
         <v>1300</v>
@@ -6270,13 +6469,13 @@
         <v>1300</v>
       </c>
       <c r="H83" s="9">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="I83" s="9">
         <v>1600</v>
       </c>
       <c r="J83" s="9">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="K83" s="9">
         <v>1700</v>
@@ -6285,47 +6484,47 @@
         <v>1700</v>
       </c>
       <c r="M83" s="9">
+        <v>1700</v>
+      </c>
+      <c r="N83" s="9">
         <v>1900</v>
-      </c>
-      <c r="N83" s="7">
-        <v>3000</v>
       </c>
       <c r="O83" s="7">
         <v>3000</v>
       </c>
       <c r="P83" s="7">
+        <v>3000</v>
+      </c>
+      <c r="Q83" s="7">
         <v>3100</v>
       </c>
-      <c r="Q83" s="7">
+      <c r="R83" s="7">
         <v>2900</v>
-      </c>
-      <c r="R83" s="7">
-        <v>2800</v>
       </c>
       <c r="S83" s="7">
         <v>2800</v>
       </c>
       <c r="T83" s="7">
+        <v>2800</v>
+      </c>
+      <c r="U83" s="7">
         <v>3000</v>
       </c>
-      <c r="U83" s="7">
+      <c r="V83" s="7">
         <v>3500</v>
       </c>
-      <c r="V83" s="4">
+      <c r="W83" s="4">
         <v>3400</v>
       </c>
-      <c r="W83" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X83" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="Y83" s="4">
+      <c r="Y83" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z83" s="4">
         <v>11200</v>
       </c>
-      <c r="Z83" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="AA83" s="4" t="s">
         <v>8</v>
       </c>
@@ -6335,8 +6534,11 @@
       <c r="AC83" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD83" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6370,7 +6572,7 @@
       <c r="M84" s="9">
         <v>0</v>
       </c>
-      <c r="N84" s="7">
+      <c r="N84" s="9">
         <v>0</v>
       </c>
       <c r="O84" s="7">
@@ -6394,7 +6596,7 @@
       <c r="U84" s="7">
         <v>0</v>
       </c>
-      <c r="V84" s="4">
+      <c r="V84" s="7">
         <v>0</v>
       </c>
       <c r="W84" s="4">
@@ -6418,8 +6620,11 @@
       <c r="AC84" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD84" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6453,7 +6658,7 @@
       <c r="M85" s="9">
         <v>0</v>
       </c>
-      <c r="N85" s="7">
+      <c r="N85" s="9">
         <v>0</v>
       </c>
       <c r="O85" s="7">
@@ -6477,7 +6682,7 @@
       <c r="U85" s="7">
         <v>0</v>
       </c>
-      <c r="V85" s="4">
+      <c r="V85" s="7">
         <v>0</v>
       </c>
       <c r="W85" s="4">
@@ -6501,8 +6706,11 @@
       <c r="AC85" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD85" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6536,7 +6744,7 @@
       <c r="M86" s="9">
         <v>0</v>
       </c>
-      <c r="N86" s="7">
+      <c r="N86" s="9">
         <v>0</v>
       </c>
       <c r="O86" s="7">
@@ -6560,7 +6768,7 @@
       <c r="U86" s="7">
         <v>0</v>
       </c>
-      <c r="V86" s="4">
+      <c r="V86" s="7">
         <v>0</v>
       </c>
       <c r="W86" s="4">
@@ -6584,8 +6792,11 @@
       <c r="AC86" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD86" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6619,7 +6830,7 @@
       <c r="M87" s="9">
         <v>0</v>
       </c>
-      <c r="N87" s="7">
+      <c r="N87" s="9">
         <v>0</v>
       </c>
       <c r="O87" s="7">
@@ -6643,7 +6854,7 @@
       <c r="U87" s="7">
         <v>0</v>
       </c>
-      <c r="V87" s="4">
+      <c r="V87" s="7">
         <v>0</v>
       </c>
       <c r="W87" s="4">
@@ -6667,8 +6878,11 @@
       <c r="AC87" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD87" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6702,7 +6916,7 @@
       <c r="M88" s="9">
         <v>0</v>
       </c>
-      <c r="N88" s="7">
+      <c r="N88" s="9">
         <v>0</v>
       </c>
       <c r="O88" s="7">
@@ -6726,7 +6940,7 @@
       <c r="U88" s="7">
         <v>0</v>
       </c>
-      <c r="V88" s="4">
+      <c r="V88" s="7">
         <v>0</v>
       </c>
       <c r="W88" s="4">
@@ -6750,80 +6964,83 @@
       <c r="AC88" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD88" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="9">
+        <v>58500</v>
+      </c>
+      <c r="E89" s="9">
         <v>62400</v>
       </c>
-      <c r="E89" s="9">
+      <c r="F89" s="9">
         <v>62300</v>
       </c>
-      <c r="F89" s="9">
+      <c r="G89" s="9">
         <v>63500</v>
       </c>
-      <c r="G89" s="9">
+      <c r="H89" s="9">
         <v>58600</v>
       </c>
-      <c r="H89" s="9">
+      <c r="I89" s="9">
         <v>58000</v>
       </c>
-      <c r="I89" s="9">
+      <c r="J89" s="9">
         <v>41400</v>
       </c>
-      <c r="J89" s="9">
+      <c r="K89" s="9">
         <v>42300</v>
       </c>
-      <c r="K89" s="9">
+      <c r="L89" s="9">
         <v>36300</v>
       </c>
-      <c r="L89" s="9">
+      <c r="M89" s="9">
         <v>40600</v>
       </c>
-      <c r="M89" s="9">
+      <c r="N89" s="9">
         <v>30900</v>
       </c>
-      <c r="N89" s="7">
+      <c r="O89" s="7">
         <v>23900</v>
       </c>
-      <c r="O89" s="7">
+      <c r="P89" s="7">
         <v>19900</v>
       </c>
-      <c r="P89" s="7">
+      <c r="Q89" s="7">
         <v>11500</v>
       </c>
-      <c r="Q89" s="7">
+      <c r="R89" s="7">
         <v>7200</v>
       </c>
-      <c r="R89" s="7">
+      <c r="S89" s="7">
         <v>-4200</v>
       </c>
-      <c r="S89" s="7">
+      <c r="T89" s="7">
         <v>-6800</v>
       </c>
-      <c r="T89" s="7">
+      <c r="U89" s="7">
         <v>1400</v>
       </c>
-      <c r="U89" s="7">
+      <c r="V89" s="7">
         <v>4800</v>
       </c>
-      <c r="V89" s="4">
+      <c r="W89" s="4">
         <v>-2000</v>
       </c>
-      <c r="W89" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X89" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="Y89" s="4">
+      <c r="Y89" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z89" s="4">
         <v>32500</v>
       </c>
-      <c r="Z89" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="AA89" s="4" t="s">
         <v>8</v>
       </c>
@@ -6833,8 +7050,11 @@
       <c r="AC89" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD89" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6848,7 +7068,7 @@
       <c r="K90" s="9"/>
       <c r="L90" s="9"/>
       <c r="M90" s="9"/>
-      <c r="N90" s="7"/>
+      <c r="N90" s="9"/>
       <c r="O90" s="7"/>
       <c r="P90" s="7"/>
       <c r="Q90" s="7"/>
@@ -6856,7 +7076,7 @@
       <c r="S90" s="7"/>
       <c r="T90" s="7"/>
       <c r="U90" s="7"/>
-      <c r="V90" s="4"/>
+      <c r="V90" s="7"/>
       <c r="W90" s="4"/>
       <c r="X90" s="4"/>
       <c r="Y90" s="4"/>
@@ -6864,80 +7084,81 @@
       <c r="AA90" s="4"/>
       <c r="AB90" s="4"/>
       <c r="AC90" s="4"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD90" s="4"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="9">
+        <v>-5000</v>
+      </c>
+      <c r="E91" s="9">
         <v>-3900</v>
       </c>
-      <c r="E91" s="9">
+      <c r="F91" s="9">
         <v>-2200</v>
       </c>
-      <c r="F91" s="9">
+      <c r="G91" s="9">
         <v>-1800</v>
       </c>
-      <c r="G91" s="9">
+      <c r="H91" s="9">
         <v>-400</v>
       </c>
-      <c r="H91" s="9">
+      <c r="I91" s="9">
         <v>-1300</v>
       </c>
-      <c r="I91" s="9">
+      <c r="J91" s="9">
         <v>-5100</v>
       </c>
-      <c r="J91" s="9">
+      <c r="K91" s="9">
         <v>-1100</v>
       </c>
-      <c r="K91" s="9">
+      <c r="L91" s="9">
         <v>-2300</v>
       </c>
-      <c r="L91" s="9">
+      <c r="M91" s="9">
         <v>-700</v>
       </c>
-      <c r="M91" s="9">
+      <c r="N91" s="9">
         <v>-1100</v>
-      </c>
-      <c r="N91" s="7">
-        <v>-1800</v>
       </c>
       <c r="O91" s="7">
         <v>-1800</v>
       </c>
       <c r="P91" s="7">
+        <v>-1800</v>
+      </c>
+      <c r="Q91" s="7">
         <v>-2400</v>
       </c>
-      <c r="Q91" s="7">
+      <c r="R91" s="7">
         <v>-3100</v>
       </c>
-      <c r="R91" s="7">
+      <c r="S91" s="7">
         <v>-1900</v>
       </c>
-      <c r="S91" s="7">
+      <c r="T91" s="7">
         <v>-2000</v>
       </c>
-      <c r="T91" s="7">
+      <c r="U91" s="7">
         <v>-1400</v>
       </c>
-      <c r="U91" s="7">
+      <c r="V91" s="7">
         <v>-1500</v>
       </c>
-      <c r="V91" s="4">
+      <c r="W91" s="4">
         <v>-1300</v>
       </c>
-      <c r="W91" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X91" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="Y91" s="4">
+      <c r="Y91" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z91" s="4">
         <v>-4400</v>
       </c>
-      <c r="Z91" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="AA91" s="4" t="s">
         <v>8</v>
       </c>
@@ -6947,8 +7168,11 @@
       <c r="AC91" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD91" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6982,7 +7206,7 @@
       <c r="M92" s="9">
         <v>0</v>
       </c>
-      <c r="N92" s="7">
+      <c r="N92" s="9">
         <v>0</v>
       </c>
       <c r="O92" s="7">
@@ -7006,7 +7230,7 @@
       <c r="U92" s="7">
         <v>0</v>
       </c>
-      <c r="V92" s="4">
+      <c r="V92" s="7">
         <v>0</v>
       </c>
       <c r="W92" s="4">
@@ -7030,8 +7254,11 @@
       <c r="AC92" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD92" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7065,7 +7292,7 @@
       <c r="M93" s="9">
         <v>0</v>
       </c>
-      <c r="N93" s="7">
+      <c r="N93" s="9">
         <v>0</v>
       </c>
       <c r="O93" s="7">
@@ -7089,7 +7316,7 @@
       <c r="U93" s="7">
         <v>0</v>
       </c>
-      <c r="V93" s="4">
+      <c r="V93" s="7">
         <v>0</v>
       </c>
       <c r="W93" s="4">
@@ -7113,80 +7340,83 @@
       <c r="AC93" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD93" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="9">
+        <v>54600</v>
+      </c>
+      <c r="E94" s="9">
         <v>-82300</v>
       </c>
-      <c r="E94" s="9">
+      <c r="F94" s="9">
         <v>157200</v>
       </c>
-      <c r="F94" s="9">
+      <c r="G94" s="9">
         <v>45500</v>
       </c>
-      <c r="G94" s="9">
+      <c r="H94" s="9">
         <v>-42800</v>
       </c>
-      <c r="H94" s="9">
+      <c r="I94" s="9">
         <v>46200</v>
       </c>
-      <c r="I94" s="9">
+      <c r="J94" s="9">
         <v>209100</v>
       </c>
-      <c r="J94" s="9">
+      <c r="K94" s="9">
         <v>50200</v>
       </c>
-      <c r="K94" s="9">
+      <c r="L94" s="9">
         <v>-182700</v>
       </c>
-      <c r="L94" s="9">
+      <c r="M94" s="9">
         <v>-37800</v>
       </c>
-      <c r="M94" s="9">
+      <c r="N94" s="9">
         <v>12200</v>
       </c>
-      <c r="N94" s="7">
+      <c r="O94" s="7">
         <v>102100</v>
       </c>
-      <c r="O94" s="7">
+      <c r="P94" s="7">
         <v>2800</v>
       </c>
-      <c r="P94" s="7">
+      <c r="Q94" s="7">
         <v>41300</v>
       </c>
-      <c r="Q94" s="7">
+      <c r="R94" s="7">
         <v>-123800</v>
       </c>
-      <c r="R94" s="7">
+      <c r="S94" s="7">
         <v>-140200</v>
       </c>
-      <c r="S94" s="7">
+      <c r="T94" s="7">
         <v>4800</v>
       </c>
-      <c r="T94" s="7">
+      <c r="U94" s="7">
         <v>-25600</v>
       </c>
-      <c r="U94" s="7">
+      <c r="V94" s="7">
         <v>-432300</v>
       </c>
-      <c r="V94" s="4">
+      <c r="W94" s="4">
         <v>10700</v>
       </c>
-      <c r="W94" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X94" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="Y94" s="4">
+      <c r="Y94" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z94" s="4">
         <v>-11400</v>
       </c>
-      <c r="Z94" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="AA94" s="4" t="s">
         <v>8</v>
       </c>
@@ -7196,8 +7426,11 @@
       <c r="AC94" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD94" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7211,7 +7444,7 @@
       <c r="K95" s="9"/>
       <c r="L95" s="9"/>
       <c r="M95" s="9"/>
-      <c r="N95" s="7"/>
+      <c r="N95" s="9"/>
       <c r="O95" s="7"/>
       <c r="P95" s="7"/>
       <c r="Q95" s="7"/>
@@ -7219,7 +7452,7 @@
       <c r="S95" s="7"/>
       <c r="T95" s="7"/>
       <c r="U95" s="7"/>
-      <c r="V95" s="4"/>
+      <c r="V95" s="7"/>
       <c r="W95" s="4"/>
       <c r="X95" s="4"/>
       <c r="Y95" s="4"/>
@@ -7227,8 +7460,9 @@
       <c r="AA95" s="4"/>
       <c r="AB95" s="4"/>
       <c r="AC95" s="4"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD95" s="4"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7262,8 +7496,8 @@
       <c r="M96" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="N96" s="7">
-        <v>0</v>
+      <c r="N96" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="O96" s="7">
         <v>0</v>
@@ -7286,7 +7520,7 @@
       <c r="U96" s="7">
         <v>0</v>
       </c>
-      <c r="V96" s="4">
+      <c r="V96" s="7">
         <v>0</v>
       </c>
       <c r="W96" s="4">
@@ -7310,8 +7544,11 @@
       <c r="AC96" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD96" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7345,7 +7582,7 @@
       <c r="M97" s="9">
         <v>0</v>
       </c>
-      <c r="N97" s="7">
+      <c r="N97" s="9">
         <v>0</v>
       </c>
       <c r="O97" s="7">
@@ -7369,7 +7606,7 @@
       <c r="U97" s="7">
         <v>0</v>
       </c>
-      <c r="V97" s="4">
+      <c r="V97" s="7">
         <v>0</v>
       </c>
       <c r="W97" s="4">
@@ -7393,8 +7630,11 @@
       <c r="AC97" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD97" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7428,7 +7668,7 @@
       <c r="M98" s="9">
         <v>0</v>
       </c>
-      <c r="N98" s="7">
+      <c r="N98" s="9">
         <v>0</v>
       </c>
       <c r="O98" s="7">
@@ -7452,7 +7692,7 @@
       <c r="U98" s="7">
         <v>0</v>
       </c>
-      <c r="V98" s="4">
+      <c r="V98" s="7">
         <v>0</v>
       </c>
       <c r="W98" s="4">
@@ -7476,8 +7716,11 @@
       <c r="AC98" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD98" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7511,7 +7754,7 @@
       <c r="M99" s="9">
         <v>0</v>
       </c>
-      <c r="N99" s="7">
+      <c r="N99" s="9">
         <v>0</v>
       </c>
       <c r="O99" s="7">
@@ -7535,7 +7778,7 @@
       <c r="U99" s="7">
         <v>0</v>
       </c>
-      <c r="V99" s="4">
+      <c r="V99" s="7">
         <v>0</v>
       </c>
       <c r="W99" s="4">
@@ -7559,80 +7802,83 @@
       <c r="AC99" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD99" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="9">
+        <v>-165800</v>
+      </c>
+      <c r="E100" s="9">
         <v>-55500</v>
       </c>
-      <c r="E100" s="9">
+      <c r="F100" s="9">
         <v>-8300</v>
       </c>
-      <c r="F100" s="9">
+      <c r="G100" s="9">
         <v>-174100</v>
       </c>
-      <c r="G100" s="9">
+      <c r="H100" s="9">
         <v>-124000</v>
       </c>
-      <c r="H100" s="9">
+      <c r="I100" s="9">
         <v>-130300</v>
       </c>
-      <c r="I100" s="9">
+      <c r="J100" s="9">
         <v>-21300</v>
       </c>
-      <c r="J100" s="9">
+      <c r="K100" s="9">
         <v>-11600</v>
       </c>
-      <c r="K100" s="9">
+      <c r="L100" s="9">
         <v>-11400</v>
       </c>
-      <c r="L100" s="9">
+      <c r="M100" s="9">
         <v>-23000</v>
       </c>
-      <c r="M100" s="9">
+      <c r="N100" s="9">
         <v>-13200</v>
       </c>
-      <c r="N100" s="7">
+      <c r="O100" s="7">
         <v>-24000</v>
       </c>
-      <c r="O100" s="7">
+      <c r="P100" s="7">
         <v>-11000</v>
       </c>
-      <c r="P100" s="7">
+      <c r="Q100" s="7">
         <v>-12400</v>
       </c>
-      <c r="Q100" s="7">
+      <c r="R100" s="7">
         <v>-11600</v>
       </c>
-      <c r="R100" s="7">
+      <c r="S100" s="7">
         <v>-13400</v>
       </c>
-      <c r="S100" s="7">
+      <c r="T100" s="7">
         <v>-11300</v>
       </c>
-      <c r="T100" s="7">
+      <c r="U100" s="7">
         <v>-120000</v>
       </c>
-      <c r="U100" s="7">
+      <c r="V100" s="7">
         <v>-4700</v>
       </c>
-      <c r="V100" s="4">
+      <c r="W100" s="4">
         <v>1065400</v>
       </c>
-      <c r="W100" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X100" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="Y100" s="4">
+      <c r="Y100" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z100" s="4">
         <v>-1900</v>
       </c>
-      <c r="Z100" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="AA100" s="4" t="s">
         <v>8</v>
       </c>
@@ -7642,8 +7888,11 @@
       <c r="AC100" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD100" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7677,8 +7926,8 @@
       <c r="M101" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="7">
-        <v>0</v>
+      <c r="N101" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="O101" s="7">
         <v>0</v>
@@ -7701,7 +7950,7 @@
       <c r="U101" s="7">
         <v>0</v>
       </c>
-      <c r="V101" s="4">
+      <c r="V101" s="7">
         <v>0</v>
       </c>
       <c r="W101" s="4">
@@ -7725,80 +7974,83 @@
       <c r="AC101" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.25">
+      <c r="AD101" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.25">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="9">
+        <v>-53500</v>
+      </c>
+      <c r="E102" s="9">
         <v>-82900</v>
       </c>
-      <c r="E102" s="9">
+      <c r="F102" s="9">
         <v>211200</v>
       </c>
-      <c r="F102" s="9">
+      <c r="G102" s="9">
         <v>-65000</v>
       </c>
-      <c r="G102" s="9">
+      <c r="H102" s="9">
         <v>-108300</v>
       </c>
-      <c r="H102" s="9">
+      <c r="I102" s="9">
         <v>-26100</v>
       </c>
-      <c r="I102" s="9">
+      <c r="J102" s="9">
         <v>229200</v>
       </c>
-      <c r="J102" s="9">
+      <c r="K102" s="9">
         <v>80800</v>
       </c>
-      <c r="K102" s="9">
+      <c r="L102" s="9">
         <v>-157800</v>
       </c>
-      <c r="L102" s="9">
+      <c r="M102" s="9">
         <v>-20100</v>
       </c>
-      <c r="M102" s="9">
+      <c r="N102" s="9">
         <v>29900</v>
       </c>
-      <c r="N102" s="7">
+      <c r="O102" s="7">
         <v>102000</v>
       </c>
-      <c r="O102" s="7">
+      <c r="P102" s="7">
         <v>11700</v>
       </c>
-      <c r="P102" s="7">
+      <c r="Q102" s="7">
         <v>40400</v>
       </c>
-      <c r="Q102" s="7">
+      <c r="R102" s="7">
         <v>-128200</v>
       </c>
-      <c r="R102" s="7">
+      <c r="S102" s="7">
         <v>-157800</v>
       </c>
-      <c r="S102" s="7">
+      <c r="T102" s="7">
         <v>-13400</v>
       </c>
-      <c r="T102" s="7">
+      <c r="U102" s="7">
         <v>-144300</v>
       </c>
-      <c r="U102" s="7">
+      <c r="V102" s="7">
         <v>-432100</v>
       </c>
-      <c r="V102" s="4">
+      <c r="W102" s="4">
         <v>1074000</v>
       </c>
-      <c r="W102" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="X102" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="Y102" s="4">
+      <c r="Y102" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z102" s="4">
         <v>19200</v>
       </c>
-      <c r="Z102" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="AA102" s="4" t="s">
         <v>8</v>
       </c>
@@ -7806,6 +8058,9 @@
         <v>8</v>
       </c>
       <c r="AC102" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD102" s="4" t="s">
         <v>8</v>
       </c>
     </row>
